--- a/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_39.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3694052.091294376</v>
+        <v>3694135.847615197</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17424111.62762216</v>
+        <v>17424111.6276223</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17424111.62762216</v>
+        <v>17424111.6276223</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4036467.59329892</v>
+        <v>4036467.593299039</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4036467.59329892</v>
+        <v>4036467.593299039</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48818732.47780251</v>
+        <v>48818732.47780246</v>
       </c>
     </row>
   </sheetData>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>27.21988704442544</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>109.2191999999999</v>
+        <v>124</v>
       </c>
       <c r="U2" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>124</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>111.535425392244</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>121.0985520093604</v>
       </c>
       <c r="S3" t="n">
-        <v>58.73324524763018</v>
+        <v>66.13141008526168</v>
       </c>
       <c r="T3" t="n">
         <v>3.658482198645913</v>
@@ -799,7 +799,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>124</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>65.22787369763188</v>
       </c>
       <c r="N4" t="n">
         <v>117.0987146159472</v>
       </c>
       <c r="O4" t="n">
-        <v>116.1204853840528</v>
+        <v>124</v>
       </c>
       <c r="P4" t="n">
         <v>124</v>
       </c>
       <c r="Q4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>50.89261168642087</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -945,19 +945,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="U5" t="n">
         <v>124</v>
       </c>
       <c r="V5" t="n">
+        <v>56.7751891684823</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
         <v>124</v>
-      </c>
-      <c r="W5" t="n">
-        <v>124</v>
-      </c>
-      <c r="X5" t="n">
-        <v>106.2497674114762</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -979,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>106.7997470864971</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>124</v>
+        <v>121.0985520093604</v>
       </c>
       <c r="S6" t="n">
-        <v>124</v>
+        <v>58.73324524763017</v>
       </c>
       <c r="T6" t="n">
         <v>3.658482198645892</v>
@@ -1030,10 +1030,10 @@
         <v>0.182623911130144</v>
       </c>
       <c r="V6" t="n">
-        <v>124</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>85.51535444483638</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>65.22787369763185</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>117.0987146159472</v>
       </c>
       <c r="O7" t="n">
-        <v>109.2191999999999</v>
+        <v>124</v>
       </c>
       <c r="P7" t="n">
         <v>124</v>
       </c>
       <c r="Q7" t="n">
-        <v>124</v>
+        <v>50.89261168642093</v>
       </c>
       <c r="R7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>73.89299192292592</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>124.7606684554556</v>
+        <v>50.86767653252969</v>
       </c>
       <c r="V8" t="n">
         <v>226.8510241668239</v>
@@ -1210,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>173.9038504532639</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>261.2478013127345</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>263</v>
       </c>
       <c r="S9" t="n">
-        <v>55.73324524763017</v>
+        <v>263</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6584821986458915</v>
+        <v>263</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>16.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>62.22787369763186</v>
       </c>
       <c r="N10" t="n">
-        <v>65.46172547795341</v>
+        <v>114.0987146159472</v>
       </c>
       <c r="O10" t="n">
         <v>187.4880558822936</v>
@@ -1331,7 +1331,7 @@
         <v>241.7006186397529</v>
       </c>
       <c r="Q10" t="n">
-        <v>263</v>
+        <v>152.1351371643744</v>
       </c>
       <c r="R10" t="n">
         <v>263</v>
@@ -1368,13 +1368,13 @@
         <v>173.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>15.0534580322682</v>
+        <v>87.58316034832551</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>96.36328960686865</v>
       </c>
       <c r="F11" t="n">
         <v>96.88962870801186</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>168.8929919229259</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>275.2263756984131</v>
@@ -1568,10 +1568,10 @@
         <v>324</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>173.3502676156238</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>48.21393871924886</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>173.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>141.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>102.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>96.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>96.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>94.96943258852374</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>91.94017126634148</v>
+        <v>3.246342372508336</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1659,19 +1659,19 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>321.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="X14" t="n">
-        <v>256.0861982090296</v>
+        <v>284.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>203.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1744,7 +1744,7 @@
         <v>106.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>122.6245861665746</v>
+        <v>122.6245861665787</v>
       </c>
       <c r="X15" t="n">
         <v>111.8627394453875</v>
@@ -1790,28 +1790,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>63.00034946925458</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>157.2278736976318</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>209.0987146159472</v>
       </c>
       <c r="O16" t="n">
-        <v>237.165261280751</v>
+        <v>282.4880558822936</v>
       </c>
       <c r="P16" t="n">
         <v>324</v>
       </c>
       <c r="Q16" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>324</v>
+        <v>221.5642063348726</v>
       </c>
       <c r="S16" t="n">
-        <v>48.21393871924888</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>86.99931295557451</v>
       </c>
       <c r="C17" t="n">
-        <v>4.987238455246052</v>
+        <v>54.47457824299391</v>
       </c>
       <c r="D17" t="n">
         <v>15.33915573984979</v>
@@ -1890,13 +1890,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>81.89299192292594</v>
       </c>
       <c r="T17" t="n">
         <v>188.2263756984131</v>
       </c>
       <c r="U17" t="n">
-        <v>254.1582613727313</v>
+        <v>6.460496979251428</v>
       </c>
       <c r="V17" t="n">
         <v>234.8510241668239</v>
@@ -1908,7 +1908,7 @@
         <v>197.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>116.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>202.6112915517259</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1966,10 +1966,10 @@
         <v>119.2643216942532</v>
       </c>
       <c r="R18" t="n">
-        <v>191.9159310975085</v>
+        <v>126.0985520093604</v>
       </c>
       <c r="S18" t="n">
-        <v>324</v>
+        <v>63.73324524763018</v>
       </c>
       <c r="T18" t="n">
         <v>8.658482198645913</v>
@@ -1984,10 +1984,10 @@
         <v>37.37314290982852</v>
       </c>
       <c r="X18" t="n">
-        <v>24.86273944538755</v>
+        <v>225.166772071497</v>
       </c>
       <c r="Y18" t="n">
-        <v>324</v>
+        <v>4.391392766134345</v>
       </c>
     </row>
     <row r="19">
@@ -2082,16 +2082,16 @@
         <v>54.47457824299391</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>15.33915573984979</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>9.363289606868648</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>9.889628708011855</v>
       </c>
       <c r="G20" t="n">
-        <v>7.668775710441706</v>
+        <v>7.969432588523773</v>
       </c>
       <c r="H20" t="n">
         <v>4.940171266341508</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>116.3174326828064</v>
+        <v>81.42470174999401</v>
       </c>
     </row>
     <row r="21">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>232.5205237287596</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R21" t="n">
         <v>126.0985520093604</v>
@@ -2212,10 +2212,10 @@
         <v>8.658482198645913</v>
       </c>
       <c r="U21" t="n">
-        <v>8.665570997627251</v>
+        <v>328</v>
       </c>
       <c r="V21" t="n">
-        <v>19.51066719152016</v>
+        <v>328</v>
       </c>
       <c r="W21" t="n">
         <v>37.37314290982852</v>
@@ -2224,7 +2224,7 @@
         <v>24.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>328</v>
+        <v>4.391392766134345</v>
       </c>
     </row>
     <row r="22">
@@ -2334,7 +2334,7 @@
         <v>7.940171266341508</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1.362235606519822</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.362235606526835</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>84.89299192292594</v>
@@ -2395,16 +2395,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>225.1788118388038</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2449,13 +2449,13 @@
         <v>11.65848219864591</v>
       </c>
       <c r="U24" t="n">
-        <v>185.8191750868682</v>
+        <v>8.182623911130122</v>
       </c>
       <c r="V24" t="n">
-        <v>399.0000000000007</v>
+        <v>22.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>399.0000000000007</v>
+        <v>40.37314290982852</v>
       </c>
       <c r="X24" t="n">
         <v>27.86273944538755</v>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>174.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>142.4745782429939</v>
+        <v>19.57508024851732</v>
       </c>
       <c r="D26" t="n">
         <v>103.3391557398498</v>
@@ -2562,13 +2562,13 @@
         <v>97.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>97.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>95.96943258852374</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>92.94017126634148</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>276.2263756984131</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>265.1267973112955</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>285.2818334606677</v>
@@ -2644,10 +2644,10 @@
         <v>32.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>18.31795096936696</v>
+        <v>18.31795096936697</v>
       </c>
       <c r="H27" t="n">
-        <v>21.09646454491173</v>
+        <v>21.0964645449117</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>212.873195266163</v>
+        <v>212.8731952661065</v>
       </c>
       <c r="S27" t="n">
         <v>151.7332452476302</v>
       </c>
       <c r="T27" t="n">
-        <v>96.65848219864591</v>
+        <v>96.65848219864588</v>
       </c>
       <c r="U27" t="n">
-        <v>93.18262391113012</v>
+        <v>93.18262391113015</v>
       </c>
       <c r="V27" t="n">
         <v>107.5106671915202</v>
@@ -2738,28 +2738,28 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>64.00034946925456</v>
+        <v>64.00034946925459</v>
       </c>
       <c r="M28" t="n">
-        <v>158.2278736976319</v>
+        <v>158.2278736976318</v>
       </c>
       <c r="N28" t="n">
-        <v>60.54764723580221</v>
+        <v>210.0987146159472</v>
       </c>
       <c r="O28" t="n">
-        <v>283.4880558822937</v>
+        <v>283.4880558822936</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>328.0000000000001</v>
+        <v>328.0000000000123</v>
       </c>
       <c r="R28" t="n">
-        <v>328.0000000000001</v>
+        <v>178.448932619843</v>
       </c>
       <c r="S28" t="n">
-        <v>49.21393871924886</v>
+        <v>49.21393871924888</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2793,19 +2793,19 @@
         <v>142.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>103.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>97.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>92.94017126634148</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,13 +2838,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>169.8929919229259</v>
       </c>
       <c r="T29" t="n">
-        <v>43.55460128602004</v>
+        <v>276.2263756984131</v>
       </c>
       <c r="U29" t="n">
-        <v>328.0000000000232</v>
+        <v>131.0871364530835</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>214.0985520093604</v>
+        <v>212.8731952661176</v>
       </c>
       <c r="S30" t="n">
         <v>151.7332452476302</v>
@@ -2929,7 +2929,7 @@
         <v>107.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>124.1477861665843</v>
+        <v>125.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>112.8627394453875</v>
@@ -2978,25 +2978,25 @@
         <v>64.00034946925459</v>
       </c>
       <c r="M31" t="n">
-        <v>158.2278736976318</v>
+        <v>13.3788009189536</v>
       </c>
       <c r="N31" t="n">
-        <v>16.03570311802129</v>
+        <v>210.0987146159472</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>328.0000000000265</v>
+        <v>328.000000000027</v>
       </c>
       <c r="Q31" t="n">
-        <v>328.0000000000286</v>
+        <v>328.0000000000291</v>
       </c>
       <c r="R31" t="n">
-        <v>328.0000000000194</v>
+        <v>328.0000000000198</v>
       </c>
       <c r="S31" t="n">
-        <v>49.21393871924888</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>118.2263756984131</v>
       </c>
       <c r="U32" t="n">
-        <v>78.4095531318975</v>
+        <v>184.1582613727313</v>
       </c>
       <c r="V32" t="n">
         <v>164.8510241668239</v>
@@ -3090,10 +3090,10 @@
         <v>173.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>127.2818334606677</v>
+        <v>84.8498708581581</v>
       </c>
       <c r="Y32" t="n">
-        <v>46.31743268280638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>190.000000000003</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3154,13 +3154,13 @@
         <v>190.000000000003</v>
       </c>
       <c r="S33" t="n">
-        <v>48.08767830579439</v>
+        <v>190.000000000003</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>48.08767830573765</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>190.000000000003</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3227,10 +3227,10 @@
         <v>179.7006186397529</v>
       </c>
       <c r="Q34" t="n">
-        <v>189.8367371643756</v>
+        <v>189.8367371643153</v>
       </c>
       <c r="R34" t="n">
-        <v>190.0000000000555</v>
+        <v>190.0000000000591</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3315,19 +3315,19 @@
         <v>11.89299192292594</v>
       </c>
       <c r="T35" t="n">
-        <v>118.2263756984131</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>129.0000000000726</v>
+        <v>40.13162897788413</v>
       </c>
       <c r="V35" t="n">
-        <v>49.18708674020314</v>
+        <v>129.0000000000731</v>
       </c>
       <c r="W35" t="n">
-        <v>129.0000000000609</v>
+        <v>129.0000000000682</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>127.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>46.31743268280638</v>
@@ -3355,13 +3355,13 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>129.0000000000055</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3388,13 +3388,13 @@
         <v>119.2643216942532</v>
       </c>
       <c r="R36" t="n">
+        <v>123.3588783057358</v>
+      </c>
+      <c r="S36" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
       <c r="T36" t="n">
-        <v>123.3588783057926</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.2278736976318783</v>
       </c>
       <c r="N37" t="n">
         <v>52.09871461594719</v>
@@ -3461,13 +3461,13 @@
         <v>125.4880558822937</v>
       </c>
       <c r="P37" t="n">
-        <v>65.0364295016719</v>
+        <v>129.0000000000881</v>
       </c>
       <c r="Q37" t="n">
-        <v>129.0000000000732</v>
+        <v>64.80855580395755</v>
       </c>
       <c r="R37" t="n">
-        <v>129.0000000000707</v>
+        <v>129.0000000000816</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>16.99931295557451</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3555,19 +3555,19 @@
         <v>118.2263756984131</v>
       </c>
       <c r="U38" t="n">
-        <v>129.0000000000985</v>
+        <v>50.90525327951885</v>
       </c>
       <c r="V38" t="n">
-        <v>129.0000000000736</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>112.5038323785456</v>
+        <v>129.0000000000935</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>127.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>46.31743268280638</v>
       </c>
     </row>
     <row r="39">
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>129.0000000000091</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>67.26032629636813</v>
       </c>
       <c r="I39" t="n">
-        <v>129.0000000000091</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>56.09855200936042</v>
       </c>
       <c r="S39" t="n">
-        <v>67.26032629642481</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -3637,10 +3637,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3692,19 +3692,19 @@
         <v>0.2278736976318569</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>52.09871461594719</v>
       </c>
       <c r="O40" t="n">
-        <v>113.3953263021118</v>
+        <v>125.4880558822936</v>
       </c>
       <c r="P40" t="n">
-        <v>129.0000000001102</v>
+        <v>129.0000000001175</v>
       </c>
       <c r="Q40" t="n">
-        <v>129.0000000001064</v>
+        <v>129.0000000001173</v>
       </c>
       <c r="R40" t="n">
-        <v>129.0000000000965</v>
+        <v>64.80855580389252</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>129.0000000000164</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3744,13 +3744,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>129.0000000000164</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>113.6231999996181</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3795,16 +3795,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>129.0000000001408</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>129.0000000001501</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>113.6231999999508</v>
       </c>
       <c r="Y41" t="n">
-        <v>129.0000000001477</v>
+        <v>129.0000000000164</v>
       </c>
     </row>
     <row r="42">
@@ -3865,25 +3865,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>129.0000000001765</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>18.98695766171484</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>129.0000000001417</v>
+        <v>129.0000000001563</v>
       </c>
       <c r="W42" t="n">
-        <v>129.0000000001467</v>
+        <v>129.0000000001613</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>129.0000000001563</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>18.98695766164931</v>
       </c>
     </row>
     <row r="43">
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>42.11380033707866</v>
       </c>
       <c r="C43" t="n">
         <v>27.72524664804467</v>
@@ -3920,13 +3920,13 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2.457167243766001</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>126.0003494692546</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>20.74204775406584</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3935,16 +3935,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>129.0000000001893</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>82.40647256148584</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>111.2139387192489</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>2.443645430107551</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>42.46535284946236</v>
       </c>
     </row>
     <row r="44">
@@ -3981,16 +3981,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="H44" t="n">
-        <v>125.0000000000355</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4032,13 +4032,13 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>125.0000000000355</v>
+        <v>110.0999999998934</v>
       </c>
       <c r="W44" t="n">
-        <v>125.0000000000355</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>110.1000000000509</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4054,22 +4054,22 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>116.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>102.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>88.32969377404622</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>94.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>83.0964645449117</v>
+        <v>7.162313101296198</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4105,10 +4105,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>125.0000000003371</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>125.0000000003515</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>125.0000000003126</v>
       </c>
     </row>
     <row r="46">
@@ -4133,7 +4133,7 @@
         <v>42.11380033707866</v>
       </c>
       <c r="C46" t="n">
-        <v>27.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -4142,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>29.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="M46" t="n">
-        <v>32.44684088408867</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>125.0000000000355</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>7.020296349338285</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>42.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.92</v>
+        <v>37.41483539840954</v>
       </c>
       <c r="C2" t="n">
         <v>9.92</v>
@@ -4351,22 +4351,22 @@
         <v>496</v>
       </c>
       <c r="T2" t="n">
-        <v>385.6775757575758</v>
+        <v>370.7474747474747</v>
       </c>
       <c r="U2" t="n">
-        <v>260.4250505050505</v>
+        <v>370.7474747474747</v>
       </c>
       <c r="V2" t="n">
-        <v>135.1725252525252</v>
+        <v>245.4949494949495</v>
       </c>
       <c r="W2" t="n">
-        <v>9.92</v>
+        <v>120.2424242424242</v>
       </c>
       <c r="X2" t="n">
-        <v>9.92</v>
+        <v>120.2424242424242</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.92</v>
+        <v>120.2424242424242</v>
       </c>
     </row>
     <row r="3">
@@ -4376,34 +4376,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="C3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="D3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="E3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="F3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="G3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="H3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="I3" t="n">
         <v>9.92</v>
       </c>
       <c r="J3" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="K3" t="n">
         <v>132.68</v>
-      </c>
-      <c r="K3" t="n">
-        <v>255.44</v>
       </c>
       <c r="L3" t="n">
         <v>255.44</v>
@@ -4412,10 +4412,10 @@
         <v>378.2</v>
       </c>
       <c r="N3" t="n">
-        <v>496</v>
+        <v>378.2</v>
       </c>
       <c r="O3" t="n">
-        <v>496</v>
+        <v>378.2</v>
       </c>
       <c r="P3" t="n">
         <v>496</v>
@@ -4427,25 +4427,25 @@
         <v>253.2092184811983</v>
       </c>
       <c r="S3" t="n">
-        <v>193.8827081300568</v>
+        <v>186.4098143546714</v>
       </c>
       <c r="T3" t="n">
-        <v>190.187271565768</v>
+        <v>182.7143777903826</v>
       </c>
       <c r="U3" t="n">
-        <v>190.0028029686668</v>
+        <v>182.5299091932815</v>
       </c>
       <c r="V3" t="n">
-        <v>175.3455633812727</v>
+        <v>167.8726696058874</v>
       </c>
       <c r="W3" t="n">
-        <v>142.6454190279106</v>
+        <v>135.1725252525252</v>
       </c>
       <c r="X3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>122.5820458507515</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>467.290345974562</v>
+        <v>9.92</v>
       </c>
       <c r="C4" t="n">
-        <v>467.290345974562</v>
+        <v>9.92</v>
       </c>
       <c r="D4" t="n">
-        <v>467.290345974562</v>
+        <v>123.2391441250001</v>
       </c>
       <c r="E4" t="n">
-        <v>467.290345974562</v>
+        <v>241.0680483364131</v>
       </c>
       <c r="F4" t="n">
-        <v>467.290345974562</v>
+        <v>363.8280483364131</v>
       </c>
       <c r="G4" t="n">
-        <v>467.290345974562</v>
+        <v>486.5880483364131</v>
       </c>
       <c r="H4" t="n">
-        <v>467.290345974562</v>
+        <v>496</v>
       </c>
       <c r="I4" t="n">
-        <v>467.290345974562</v>
+        <v>496</v>
       </c>
       <c r="J4" t="n">
-        <v>467.290345974562</v>
+        <v>496</v>
       </c>
       <c r="K4" t="n">
-        <v>467.290345974562</v>
+        <v>496</v>
       </c>
       <c r="L4" t="n">
         <v>496</v>
       </c>
       <c r="M4" t="n">
-        <v>496</v>
+        <v>430.1132588912809</v>
       </c>
       <c r="N4" t="n">
-        <v>377.7184700849018</v>
+        <v>311.8317289761827</v>
       </c>
       <c r="O4" t="n">
-        <v>260.4250505050505</v>
+        <v>186.5792037236575</v>
       </c>
       <c r="P4" t="n">
-        <v>135.1725252525252</v>
+        <v>61.3266784711322</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.92</v>
+        <v>61.3266784711322</v>
       </c>
       <c r="R4" t="n">
         <v>9.92</v>
       </c>
       <c r="S4" t="n">
-        <v>53.26820066794363</v>
+        <v>9.92</v>
       </c>
       <c r="T4" t="n">
-        <v>176.0282006679436</v>
+        <v>9.92</v>
       </c>
       <c r="U4" t="n">
-        <v>176.0282006679436</v>
+        <v>9.92</v>
       </c>
       <c r="V4" t="n">
-        <v>221.770345974562</v>
+        <v>9.92</v>
       </c>
       <c r="W4" t="n">
-        <v>344.530345974562</v>
+        <v>9.92</v>
       </c>
       <c r="X4" t="n">
-        <v>467.290345974562</v>
+        <v>9.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>467.290345974562</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="5">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.9194268570947</v>
+        <v>62.89374831466431</v>
       </c>
       <c r="C5" t="n">
         <v>12.9194268570947</v>
@@ -4570,13 +4570,13 @@
         <v>263.4206624103253</v>
       </c>
       <c r="N5" t="n">
-        <v>263.4206624103253</v>
+        <v>311.3540057527234</v>
       </c>
       <c r="O5" t="n">
-        <v>325.3066566576019</v>
+        <v>373.24</v>
       </c>
       <c r="P5" t="n">
-        <v>437.1961136494882</v>
+        <v>496</v>
       </c>
       <c r="Q5" t="n">
         <v>496</v>
@@ -4588,22 +4588,22 @@
         <v>496</v>
       </c>
       <c r="T5" t="n">
-        <v>496</v>
+        <v>370.7474747474747</v>
       </c>
       <c r="U5" t="n">
-        <v>370.7474747474747</v>
+        <v>245.4949494949495</v>
       </c>
       <c r="V5" t="n">
-        <v>245.4949494949495</v>
+        <v>188.1462735671896</v>
       </c>
       <c r="W5" t="n">
-        <v>120.2424242424242</v>
+        <v>188.1462735671896</v>
       </c>
       <c r="X5" t="n">
-        <v>12.9194268570947</v>
+        <v>62.89374831466431</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.9194268570947</v>
+        <v>62.89374831466431</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.92</v>
+        <v>243.0510576631284</v>
       </c>
       <c r="C6" t="n">
-        <v>9.92</v>
+        <v>243.0510576631284</v>
       </c>
       <c r="D6" t="n">
-        <v>9.92</v>
+        <v>243.0510576631284</v>
       </c>
       <c r="E6" t="n">
-        <v>9.92</v>
+        <v>135.1725252525252</v>
       </c>
       <c r="F6" t="n">
         <v>9.92</v>
@@ -4637,22 +4637,22 @@
         <v>9.92</v>
       </c>
       <c r="J6" t="n">
-        <v>127.72</v>
+        <v>132.68</v>
       </c>
       <c r="K6" t="n">
-        <v>127.72</v>
+        <v>132.68</v>
       </c>
       <c r="L6" t="n">
-        <v>127.72</v>
+        <v>132.68</v>
       </c>
       <c r="M6" t="n">
-        <v>250.48</v>
+        <v>255.44</v>
       </c>
       <c r="N6" t="n">
-        <v>373.24</v>
+        <v>378.2</v>
       </c>
       <c r="O6" t="n">
-        <v>373.24</v>
+        <v>496</v>
       </c>
       <c r="P6" t="n">
         <v>496</v>
@@ -4661,28 +4661,28 @@
         <v>496</v>
       </c>
       <c r="R6" t="n">
-        <v>370.7474747474747</v>
+        <v>373.6782302935753</v>
       </c>
       <c r="S6" t="n">
-        <v>245.4949494949495</v>
+        <v>314.3517199424338</v>
       </c>
       <c r="T6" t="n">
-        <v>241.7995129306607</v>
+        <v>310.656283378145</v>
       </c>
       <c r="U6" t="n">
-        <v>241.6150443335595</v>
+        <v>310.4718147810438</v>
       </c>
       <c r="V6" t="n">
-        <v>116.3625190810343</v>
+        <v>295.8145751936497</v>
       </c>
       <c r="W6" t="n">
-        <v>29.98337317715914</v>
+        <v>263.1144308402876</v>
       </c>
       <c r="X6" t="n">
-        <v>9.92</v>
+        <v>243.0510576631284</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.92</v>
+        <v>243.0510576631284</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>496</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="C7" t="n">
-        <v>496</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="E7" t="n">
-        <v>496</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="F7" t="n">
-        <v>496</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="G7" t="n">
-        <v>496</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="H7" t="n">
-        <v>496</v>
+        <v>221.7703459745621</v>
       </c>
       <c r="I7" t="n">
-        <v>496</v>
+        <v>344.5303459745621</v>
       </c>
       <c r="J7" t="n">
-        <v>496</v>
+        <v>344.5303459745621</v>
       </c>
       <c r="K7" t="n">
-        <v>496</v>
+        <v>467.2903459745621</v>
       </c>
       <c r="L7" t="n">
         <v>496</v>
       </c>
       <c r="M7" t="n">
-        <v>496</v>
+        <v>430.113258891281</v>
       </c>
       <c r="N7" t="n">
-        <v>496</v>
+        <v>311.8317289761828</v>
       </c>
       <c r="O7" t="n">
-        <v>385.6775757575758</v>
+        <v>186.5792037236575</v>
       </c>
       <c r="P7" t="n">
-        <v>260.4250505050505</v>
+        <v>61.32667847113225</v>
       </c>
       <c r="Q7" t="n">
-        <v>135.1725252525252</v>
+        <v>9.92</v>
       </c>
       <c r="R7" t="n">
         <v>9.92</v>
       </c>
       <c r="S7" t="n">
-        <v>9.92</v>
+        <v>53.26820066794361</v>
       </c>
       <c r="T7" t="n">
-        <v>15.96266233370788</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="U7" t="n">
-        <v>138.7226623337079</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="V7" t="n">
-        <v>138.7226623337079</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="W7" t="n">
-        <v>261.4826623337079</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="X7" t="n">
-        <v>384.2426623337079</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="Y7" t="n">
-        <v>384.2426623337079</v>
+        <v>176.0282006679436</v>
       </c>
     </row>
     <row r="8">
@@ -4804,16 +4804,16 @@
         <v>274.8800284404762</v>
       </c>
       <c r="M8" t="n">
-        <v>357.4845487608372</v>
+        <v>535.2500284404762</v>
       </c>
       <c r="N8" t="n">
-        <v>617.8545487608372</v>
+        <v>795.6200284404762</v>
       </c>
       <c r="O8" t="n">
-        <v>679.7405430081138</v>
+        <v>857.5060226877528</v>
       </c>
       <c r="P8" t="n">
-        <v>791.63</v>
+        <v>969.3954796796389</v>
       </c>
       <c r="Q8" t="n">
         <v>1052</v>
@@ -4822,10 +4822,10 @@
         <v>1052</v>
       </c>
       <c r="S8" t="n">
-        <v>1052</v>
+        <v>977.3606142192667</v>
       </c>
       <c r="T8" t="n">
-        <v>1052</v>
+        <v>977.3606142192667</v>
       </c>
       <c r="U8" t="n">
         <v>925.979122772267</v>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>284.9266679926612</v>
+        <v>196.7004550032969</v>
       </c>
       <c r="C9" t="n">
-        <v>284.9266679926612</v>
+        <v>21.04</v>
       </c>
       <c r="D9" t="n">
-        <v>284.9266679926612</v>
+        <v>21.04</v>
       </c>
       <c r="E9" t="n">
         <v>21.04</v>
@@ -4874,19 +4874,19 @@
         <v>21.04</v>
       </c>
       <c r="J9" t="n">
-        <v>21.04</v>
+        <v>184.4287431941669</v>
       </c>
       <c r="K9" t="n">
-        <v>277.6287659057041</v>
+        <v>441.0175090998709</v>
       </c>
       <c r="L9" t="n">
-        <v>357.9666381778744</v>
+        <v>441.0175090998709</v>
       </c>
       <c r="M9" t="n">
-        <v>549.7989799207336</v>
+        <v>632.8498508427301</v>
       </c>
       <c r="N9" t="n">
-        <v>791.63</v>
+        <v>874.6808709219965</v>
       </c>
       <c r="O9" t="n">
         <v>1052</v>
@@ -4895,31 +4895,31 @@
         <v>1052</v>
       </c>
       <c r="Q9" t="n">
-        <v>931.5309881876231</v>
+        <v>1052</v>
       </c>
       <c r="R9" t="n">
-        <v>665.8744225310575</v>
+        <v>786.3434343434344</v>
       </c>
       <c r="S9" t="n">
-        <v>609.5782152102189</v>
+        <v>520.6868686868688</v>
       </c>
       <c r="T9" t="n">
-        <v>608.9130816762331</v>
+        <v>255.0303030303032</v>
       </c>
       <c r="U9" t="n">
-        <v>608.9130816762331</v>
+        <v>255.0303030303032</v>
       </c>
       <c r="V9" t="n">
-        <v>597.286145119142</v>
+        <v>243.4033664732121</v>
       </c>
       <c r="W9" t="n">
-        <v>567.6163037960829</v>
+        <v>213.733525150153</v>
       </c>
       <c r="X9" t="n">
-        <v>550.5832336492268</v>
+        <v>196.7004550032969</v>
       </c>
       <c r="Y9" t="n">
-        <v>284.9266679926612</v>
+        <v>196.7004550032969</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>551.6931021698169</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="C10" t="n">
-        <v>551.6931021698169</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="D10" t="n">
-        <v>551.6931021698169</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="E10" t="n">
-        <v>551.6931021698169</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="F10" t="n">
-        <v>679.0240747617524</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="G10" t="n">
-        <v>679.0240747617524</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="H10" t="n">
-        <v>854.6216618883632</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="I10" t="n">
-        <v>866.3329415458904</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="J10" t="n">
-        <v>866.3329415458904</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="K10" t="n">
         <v>1020.320345974562</v>
@@ -4962,16 +4962,16 @@
         <v>1052</v>
       </c>
       <c r="M10" t="n">
-        <v>1052</v>
+        <v>989.143561921584</v>
       </c>
       <c r="N10" t="n">
-        <v>985.8770449717642</v>
+        <v>873.8923350367888</v>
       </c>
       <c r="O10" t="n">
-        <v>796.4951703431848</v>
+        <v>684.5104604082094</v>
       </c>
       <c r="P10" t="n">
-        <v>552.3531313131314</v>
+        <v>440.368421378156</v>
       </c>
       <c r="Q10" t="n">
         <v>286.6965656565657</v>
@@ -4980,25 +4980,25 @@
         <v>21.04</v>
       </c>
       <c r="S10" t="n">
-        <v>21.04</v>
+        <v>67.35820066794361</v>
       </c>
       <c r="T10" t="n">
-        <v>21.04</v>
+        <v>240.1269652648192</v>
       </c>
       <c r="U10" t="n">
-        <v>21.04</v>
+        <v>489.6672438047452</v>
       </c>
       <c r="V10" t="n">
-        <v>222.8313928859459</v>
+        <v>691.4586366906912</v>
       </c>
       <c r="W10" t="n">
-        <v>397.6923111456234</v>
+        <v>866.3195549503686</v>
       </c>
       <c r="X10" t="n">
-        <v>551.6931021698169</v>
+        <v>1020.320345974562</v>
       </c>
       <c r="Y10" t="n">
-        <v>551.6931021698169</v>
+        <v>1020.320345974562</v>
       </c>
     </row>
     <row r="11">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>138.9938249901819</v>
+        <v>309.5928067305111</v>
       </c>
       <c r="C11" t="n">
-        <v>123.7883118262746</v>
+        <v>221.1249679948288</v>
       </c>
       <c r="D11" t="n">
-        <v>123.7883118262746</v>
+        <v>221.1249679948288</v>
       </c>
       <c r="E11" t="n">
         <v>123.7883118262746</v>
@@ -5032,25 +5032,25 @@
         <v>25.92</v>
       </c>
       <c r="J11" t="n">
-        <v>346.68</v>
+        <v>57.43406683243596</v>
       </c>
       <c r="K11" t="n">
-        <v>445.9065955778894</v>
+        <v>378.1940668324359</v>
       </c>
       <c r="L11" t="n">
-        <v>569.0059616080401</v>
+        <v>501.2934328625867</v>
       </c>
       <c r="M11" t="n">
-        <v>569.0059616080401</v>
+        <v>822.0534328625868</v>
       </c>
       <c r="N11" t="n">
-        <v>801.4645487608373</v>
+        <v>1122.224548760837</v>
       </c>
       <c r="O11" t="n">
-        <v>863.3505430081138</v>
+        <v>1184.110543008114</v>
       </c>
       <c r="P11" t="n">
-        <v>975.24</v>
+        <v>1296</v>
       </c>
       <c r="Q11" t="n">
         <v>1296</v>
@@ -5059,25 +5059,25 @@
         <v>1296</v>
       </c>
       <c r="S11" t="n">
-        <v>1125.401018259671</v>
+        <v>1296</v>
       </c>
       <c r="T11" t="n">
-        <v>847.3945781602636</v>
+        <v>1017.993559900593</v>
       </c>
       <c r="U11" t="n">
-        <v>520.1218508875363</v>
+        <v>690.7208326278655</v>
       </c>
       <c r="V11" t="n">
-        <v>520.1218508875363</v>
+        <v>690.7208326278655</v>
       </c>
       <c r="W11" t="n">
-        <v>520.1218508875363</v>
+        <v>690.7208326278655</v>
       </c>
       <c r="X11" t="n">
-        <v>520.1218508875363</v>
+        <v>690.7208326278655</v>
       </c>
       <c r="Y11" t="n">
-        <v>314.7507067634895</v>
+        <v>485.3496885038187</v>
       </c>
     </row>
     <row r="12">
@@ -5120,10 +5120,10 @@
         <v>766.657509099871</v>
       </c>
       <c r="M12" t="n">
-        <v>766.657509099871</v>
+        <v>958.4898508427302</v>
       </c>
       <c r="N12" t="n">
-        <v>1008.488529179137</v>
+        <v>1200.320870921997</v>
       </c>
       <c r="O12" t="n">
         <v>1296</v>
@@ -5211,7 +5211,7 @@
         <v>249.7222286210835</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.62094820126148</v>
+        <v>249.7222286210835</v>
       </c>
       <c r="R13" t="n">
         <v>74.62094820126148</v>
@@ -5226,10 +5226,10 @@
         <v>279.9010199938128</v>
       </c>
       <c r="V13" t="n">
-        <v>387.6424128797588</v>
+        <v>357.5613371179088</v>
       </c>
       <c r="W13" t="n">
-        <v>468.4533311394362</v>
+        <v>438.3722553775862</v>
       </c>
       <c r="X13" t="n">
         <v>498.3230464017797</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>656.1990466187772</v>
+        <v>29.19913370960438</v>
       </c>
       <c r="C14" t="n">
-        <v>513.2954322319147</v>
+        <v>29.19913370960438</v>
       </c>
       <c r="D14" t="n">
-        <v>409.9225476462078</v>
+        <v>29.19913370960438</v>
       </c>
       <c r="E14" t="n">
-        <v>312.5858914776536</v>
+        <v>29.19913370960438</v>
       </c>
       <c r="F14" t="n">
-        <v>214.717579651379</v>
+        <v>29.19913370960438</v>
       </c>
       <c r="G14" t="n">
-        <v>118.7888598649914</v>
+        <v>29.19913370960438</v>
       </c>
       <c r="H14" t="n">
         <v>25.92</v>
@@ -5269,25 +5269,25 @@
         <v>25.92</v>
       </c>
       <c r="J14" t="n">
-        <v>346.68</v>
+        <v>57.43406683243596</v>
       </c>
       <c r="K14" t="n">
-        <v>445.9065955778894</v>
+        <v>156.6606624103254</v>
       </c>
       <c r="L14" t="n">
-        <v>569.0059616080401</v>
+        <v>279.7600284404761</v>
       </c>
       <c r="M14" t="n">
-        <v>801.4645487608373</v>
+        <v>600.5200284404762</v>
       </c>
       <c r="N14" t="n">
-        <v>1122.224548760837</v>
+        <v>921.2800284404761</v>
       </c>
       <c r="O14" t="n">
-        <v>1184.110543008114</v>
+        <v>983.1660226877527</v>
       </c>
       <c r="P14" t="n">
-        <v>1296</v>
+        <v>1095.055479679639</v>
       </c>
       <c r="Q14" t="n">
         <v>1296</v>
@@ -5302,19 +5302,19 @@
         <v>1296</v>
       </c>
       <c r="U14" t="n">
-        <v>1296</v>
+        <v>968.7272727272727</v>
       </c>
       <c r="V14" t="n">
-        <v>1296</v>
+        <v>643.6252281143193</v>
       </c>
       <c r="W14" t="n">
-        <v>1296</v>
+        <v>316.352500841592</v>
       </c>
       <c r="X14" t="n">
-        <v>1037.327072516132</v>
+        <v>29.19913370960438</v>
       </c>
       <c r="Y14" t="n">
-        <v>831.9559283920847</v>
+        <v>29.19913370960438</v>
       </c>
     </row>
     <row r="15">
@@ -5369,22 +5369,22 @@
         <v>1296</v>
       </c>
       <c r="Q15" t="n">
-        <v>1296</v>
+        <v>1296.000000000004</v>
       </c>
       <c r="R15" t="n">
-        <v>1080.748937364282</v>
+        <v>1080.748937364287</v>
       </c>
       <c r="S15" t="n">
-        <v>928.493134083848</v>
+        <v>928.4931340838521</v>
       </c>
       <c r="T15" t="n">
-        <v>831.8684045902662</v>
+        <v>831.8684045902703</v>
       </c>
       <c r="U15" t="n">
-        <v>738.7546430638721</v>
+        <v>738.7546430638762</v>
       </c>
       <c r="V15" t="n">
-        <v>631.1681105471851</v>
+        <v>631.1681105471891</v>
       </c>
       <c r="W15" t="n">
         <v>507.3048921971097</v>
@@ -5424,34 +5424,34 @@
         <v>830.8258484659556</v>
       </c>
       <c r="I16" t="n">
-        <v>971.4014211725303</v>
+        <v>941.3203454106803</v>
       </c>
       <c r="J16" t="n">
-        <v>1266.143671333178</v>
+        <v>1236.062595571328</v>
       </c>
       <c r="K16" t="n">
         <v>1296</v>
       </c>
       <c r="L16" t="n">
-        <v>1296</v>
+        <v>1232.363283364389</v>
       </c>
       <c r="M16" t="n">
-        <v>1296</v>
+        <v>1073.547249326377</v>
       </c>
       <c r="N16" t="n">
-        <v>1296</v>
+        <v>862.3364264819862</v>
       </c>
       <c r="O16" t="n">
-        <v>1056.439130019443</v>
+        <v>576.9949558938108</v>
       </c>
       <c r="P16" t="n">
-        <v>729.1664027467161</v>
+        <v>249.7222286210835</v>
       </c>
       <c r="Q16" t="n">
-        <v>401.8936754739888</v>
+        <v>249.7222286210835</v>
       </c>
       <c r="R16" t="n">
-        <v>74.6209482012615</v>
+        <v>25.92</v>
       </c>
       <c r="S16" t="n">
         <v>25.92</v>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78.93910743923396</v>
+        <v>128.92631934605</v>
       </c>
       <c r="C17" t="n">
         <v>73.90149283797533</v>
@@ -5506,16 +5506,16 @@
         <v>25.92</v>
       </c>
       <c r="J17" t="n">
-        <v>346.68</v>
+        <v>57.43406683243596</v>
       </c>
       <c r="K17" t="n">
-        <v>445.9065955778894</v>
+        <v>156.6606624103254</v>
       </c>
       <c r="L17" t="n">
-        <v>569.0059616080401</v>
+        <v>279.7600284404761</v>
       </c>
       <c r="M17" t="n">
-        <v>569.0059616080401</v>
+        <v>600.5200284404762</v>
       </c>
       <c r="N17" t="n">
         <v>801.4645487608373</v>
@@ -5533,25 +5533,25 @@
         <v>1296</v>
       </c>
       <c r="S17" t="n">
-        <v>1296</v>
+        <v>1213.279806138459</v>
       </c>
       <c r="T17" t="n">
-        <v>1105.872347779381</v>
+        <v>1023.152153917839</v>
       </c>
       <c r="U17" t="n">
-        <v>849.146831241268</v>
+        <v>1016.626399393343</v>
       </c>
       <c r="V17" t="n">
-        <v>611.9235745071024</v>
+        <v>779.4031426591774</v>
       </c>
       <c r="W17" t="n">
-        <v>366.0917805869534</v>
+        <v>533.5713487390284</v>
       </c>
       <c r="X17" t="n">
-        <v>166.8172013337537</v>
+        <v>334.2967694858287</v>
       </c>
       <c r="Y17" t="n">
-        <v>166.8172013337537</v>
+        <v>216.8044132405697</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>230.5778702542686</v>
+        <v>353.1927272727273</v>
       </c>
       <c r="C18" t="n">
-        <v>230.5778702542686</v>
+        <v>353.1927272727273</v>
       </c>
       <c r="D18" t="n">
-        <v>230.5778702542686</v>
+        <v>353.1927272727273</v>
       </c>
       <c r="E18" t="n">
-        <v>230.5778702542686</v>
+        <v>25.92</v>
       </c>
       <c r="F18" t="n">
-        <v>230.5778702542686</v>
+        <v>25.92</v>
       </c>
       <c r="G18" t="n">
-        <v>230.5778702542686</v>
+        <v>25.92</v>
       </c>
       <c r="H18" t="n">
-        <v>230.5778702542686</v>
+        <v>25.92</v>
       </c>
       <c r="I18" t="n">
         <v>25.92</v>
@@ -5588,19 +5588,19 @@
         <v>189.3087431941669</v>
       </c>
       <c r="K18" t="n">
-        <v>445.897509099871</v>
+        <v>189.3087431941669</v>
       </c>
       <c r="L18" t="n">
-        <v>445.897509099871</v>
+        <v>510.0687431941669</v>
       </c>
       <c r="M18" t="n">
-        <v>637.7298508427302</v>
+        <v>701.9010849370261</v>
       </c>
       <c r="N18" t="n">
-        <v>879.5608709219966</v>
+        <v>943.7321050162925</v>
       </c>
       <c r="O18" t="n">
-        <v>1103.77147137955</v>
+        <v>1264.492105016292</v>
       </c>
       <c r="P18" t="n">
         <v>1296</v>
@@ -5609,28 +5609,28 @@
         <v>1175.530988187623</v>
       </c>
       <c r="R18" t="n">
-        <v>981.6765123315538</v>
+        <v>1048.158713430693</v>
       </c>
       <c r="S18" t="n">
-        <v>654.4037850588265</v>
+        <v>983.7816980290467</v>
       </c>
       <c r="T18" t="n">
-        <v>645.6578434440327</v>
+        <v>975.0357564142528</v>
       </c>
       <c r="U18" t="n">
-        <v>640.4228697964264</v>
+        <v>969.8007827666465</v>
       </c>
       <c r="V18" t="n">
-        <v>620.7151251585273</v>
+        <v>950.0930381287474</v>
       </c>
       <c r="W18" t="n">
-        <v>582.96447575466</v>
+        <v>912.3423887248802</v>
       </c>
       <c r="X18" t="n">
-        <v>557.8505975269959</v>
+        <v>684.9012048142771</v>
       </c>
       <c r="Y18" t="n">
-        <v>230.5778702542686</v>
+        <v>680.4654545454546</v>
       </c>
     </row>
     <row r="19">
@@ -5640,19 +5640,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>682.5424907540578</v>
+        <v>880.8926813887751</v>
       </c>
       <c r="C19" t="n">
-        <v>803.5944965724935</v>
+        <v>1001.944687207211</v>
       </c>
       <c r="D19" t="n">
-        <v>911.9636406974936</v>
+        <v>1001.944687207211</v>
       </c>
       <c r="E19" t="n">
-        <v>1024.842544908907</v>
+        <v>1114.823591418624</v>
       </c>
       <c r="F19" t="n">
-        <v>1144.253517500842</v>
+        <v>1234.234564010559</v>
       </c>
       <c r="G19" t="n">
         <v>1293.059991584449</v>
@@ -5691,25 +5691,25 @@
         <v>25.92</v>
       </c>
       <c r="S19" t="n">
-        <v>64.31820066794363</v>
+        <v>25.92</v>
       </c>
       <c r="T19" t="n">
-        <v>248.9389421218305</v>
+        <v>25.92</v>
       </c>
       <c r="U19" t="n">
-        <v>381.8637602018197</v>
+        <v>267.540278539926</v>
       </c>
       <c r="V19" t="n">
-        <v>575.7351530877656</v>
+        <v>461.4116714258719</v>
       </c>
       <c r="W19" t="n">
-        <v>575.7351530877656</v>
+        <v>628.3525896855493</v>
       </c>
       <c r="X19" t="n">
-        <v>575.7351530877656</v>
+        <v>774.4333807097429</v>
       </c>
       <c r="Y19" t="n">
-        <v>575.7351530877656</v>
+        <v>880.8926813887751</v>
       </c>
     </row>
     <row r="20">
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94.00113658563347</v>
+        <v>129.24631934605</v>
       </c>
       <c r="C20" t="n">
-        <v>38.97631007755881</v>
+        <v>74.22149283797533</v>
       </c>
       <c r="D20" t="n">
-        <v>38.97631007755881</v>
+        <v>58.72739613105635</v>
       </c>
       <c r="E20" t="n">
-        <v>38.97631007755881</v>
+        <v>49.26952784129004</v>
       </c>
       <c r="F20" t="n">
-        <v>38.97631007755881</v>
+        <v>39.28000389380332</v>
       </c>
       <c r="G20" t="n">
         <v>31.23007198620355</v>
@@ -5746,22 +5746,22 @@
         <v>57.75406683243596</v>
       </c>
       <c r="K20" t="n">
-        <v>156.9806624103254</v>
+        <v>382.4740668324359</v>
       </c>
       <c r="L20" t="n">
-        <v>280.0800284404762</v>
+        <v>505.5734328625867</v>
       </c>
       <c r="M20" t="n">
-        <v>604.8000284404761</v>
+        <v>830.2934328625872</v>
       </c>
       <c r="N20" t="n">
-        <v>813.5045487608372</v>
+        <v>1138.224548760837</v>
       </c>
       <c r="O20" t="n">
-        <v>875.3905430081138</v>
+        <v>1200.110543008114</v>
       </c>
       <c r="P20" t="n">
-        <v>987.28</v>
+        <v>1312</v>
       </c>
       <c r="Q20" t="n">
         <v>1312</v>
@@ -5788,7 +5788,7 @@
         <v>299.3715867254122</v>
       </c>
       <c r="Y20" t="n">
-        <v>181.8792304801532</v>
+        <v>217.1244132405697</v>
       </c>
     </row>
     <row r="21">
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>357.5531313131314</v>
+        <v>261.109215887636</v>
       </c>
       <c r="C21" t="n">
-        <v>26.24</v>
+        <v>261.109215887636</v>
       </c>
       <c r="D21" t="n">
-        <v>26.24</v>
+        <v>261.109215887636</v>
       </c>
       <c r="E21" t="n">
         <v>26.24</v>
@@ -5828,46 +5828,46 @@
         <v>446.217509099871</v>
       </c>
       <c r="L21" t="n">
-        <v>446.217509099871</v>
+        <v>603.2191296366907</v>
       </c>
       <c r="M21" t="n">
-        <v>638.0498508427302</v>
+        <v>795.0514713795499</v>
       </c>
       <c r="N21" t="n">
-        <v>879.8808709219966</v>
+        <v>795.0514713795499</v>
       </c>
       <c r="O21" t="n">
-        <v>1204.600870921997</v>
+        <v>1119.77147137955</v>
       </c>
       <c r="P21" t="n">
         <v>1312</v>
       </c>
       <c r="Q21" t="n">
-        <v>1312</v>
+        <v>1191.530988187623</v>
       </c>
       <c r="R21" t="n">
-        <v>1184.62772524307</v>
+        <v>1064.158713430693</v>
       </c>
       <c r="S21" t="n">
-        <v>1120.250709841423</v>
+        <v>999.7816980290467</v>
       </c>
       <c r="T21" t="n">
-        <v>1111.50476822663</v>
+        <v>991.0357564142528</v>
       </c>
       <c r="U21" t="n">
-        <v>1102.751666208824</v>
+        <v>659.7226251011214</v>
       </c>
       <c r="V21" t="n">
-        <v>1083.043921570925</v>
+        <v>328.40949378799</v>
       </c>
       <c r="W21" t="n">
-        <v>1045.293272167058</v>
+        <v>290.6588443841228</v>
       </c>
       <c r="X21" t="n">
-        <v>1020.179393939394</v>
+        <v>265.5449661564586</v>
       </c>
       <c r="Y21" t="n">
-        <v>688.8662626262627</v>
+        <v>261.109215887636</v>
       </c>
     </row>
     <row r="22">
@@ -5877,34 +5877,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>580.3632992135471</v>
+        <v>798.4569722023318</v>
       </c>
       <c r="C22" t="n">
-        <v>580.3632992135471</v>
+        <v>798.4569722023318</v>
       </c>
       <c r="D22" t="n">
-        <v>580.3632992135471</v>
+        <v>798.4569722023318</v>
       </c>
       <c r="E22" t="n">
-        <v>580.3632992135471</v>
+        <v>798.4569722023318</v>
       </c>
       <c r="F22" t="n">
-        <v>580.3632992135471</v>
+        <v>917.8679447942674</v>
       </c>
       <c r="G22" t="n">
-        <v>729.1697732971536</v>
+        <v>1066.674418877874</v>
       </c>
       <c r="H22" t="n">
-        <v>896.8473604237643</v>
+        <v>1066.674418877874</v>
       </c>
       <c r="I22" t="n">
-        <v>1123.552933130339</v>
+        <v>1293.379991584449</v>
       </c>
       <c r="J22" t="n">
-        <v>1123.552933130339</v>
+        <v>1293.379991584449</v>
       </c>
       <c r="K22" t="n">
-        <v>1269.620337559011</v>
+        <v>1293.379991584449</v>
       </c>
       <c r="L22" t="n">
         <v>1293.379991584449</v>
@@ -5928,25 +5928,25 @@
         <v>26.24</v>
       </c>
       <c r="S22" t="n">
-        <v>64.63820066794364</v>
+        <v>26.24</v>
       </c>
       <c r="T22" t="n">
-        <v>64.63820066794364</v>
+        <v>26.24</v>
       </c>
       <c r="U22" t="n">
-        <v>306.2584792078696</v>
+        <v>267.860278539926</v>
       </c>
       <c r="V22" t="n">
-        <v>367.0966608682227</v>
+        <v>461.7316714258719</v>
       </c>
       <c r="W22" t="n">
-        <v>367.0966608682227</v>
+        <v>545.5688435118461</v>
       </c>
       <c r="X22" t="n">
-        <v>367.0966608682227</v>
+        <v>691.6496345360397</v>
       </c>
       <c r="Y22" t="n">
-        <v>473.5559615472549</v>
+        <v>691.6496345360397</v>
       </c>
     </row>
     <row r="23">
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>153.1081375278682</v>
+        <v>154.4841330900094</v>
       </c>
       <c r="C23" t="n">
-        <v>95.05300798949048</v>
+        <v>96.42900355163172</v>
       </c>
       <c r="D23" t="n">
-        <v>76.52860825226847</v>
+        <v>77.90460381440971</v>
       </c>
       <c r="E23" t="n">
-        <v>64.04043693219913</v>
+        <v>65.41643249434037</v>
       </c>
       <c r="F23" t="n">
-        <v>51.02060995440938</v>
+        <v>52.39660551655061</v>
       </c>
       <c r="G23" t="n">
-        <v>39.94037501650658</v>
+        <v>41.31637057864781</v>
       </c>
       <c r="H23" t="n">
-        <v>31.92</v>
+        <v>33.29599556214124</v>
       </c>
       <c r="I23" t="n">
         <v>31.92</v>
@@ -5983,49 +5983,49 @@
         <v>63.43406683243596</v>
       </c>
       <c r="K23" t="n">
-        <v>162.6606624103254</v>
+        <v>458.4440668324359</v>
       </c>
       <c r="L23" t="n">
-        <v>285.7600284404762</v>
+        <v>581.5434328625867</v>
       </c>
       <c r="M23" t="n">
-        <v>632.2045487608432</v>
+        <v>976.5534328625874</v>
       </c>
       <c r="N23" t="n">
-        <v>1027.214548760844</v>
+        <v>1371.563432862588</v>
       </c>
       <c r="O23" t="n">
-        <v>1089.10054300812</v>
+        <v>1433.449427109865</v>
       </c>
       <c r="P23" t="n">
-        <v>1200.990000000007</v>
+        <v>1545.338884101751</v>
       </c>
       <c r="Q23" t="n">
-        <v>1596.000000000007</v>
+        <v>1596</v>
       </c>
       <c r="R23" t="n">
-        <v>1594.624004437859</v>
+        <v>1596</v>
       </c>
       <c r="S23" t="n">
-        <v>1508.873507546014</v>
+        <v>1510.249503108156</v>
       </c>
       <c r="T23" t="n">
-        <v>1315.715552295092</v>
+        <v>1317.091547857233</v>
       </c>
       <c r="U23" t="n">
-        <v>1055.959732726677</v>
+        <v>1057.335728288818</v>
       </c>
       <c r="V23" t="n">
-        <v>815.7061729622078</v>
+        <v>817.082168524349</v>
       </c>
       <c r="W23" t="n">
-        <v>566.8440760117558</v>
+        <v>568.2200715738969</v>
       </c>
       <c r="X23" t="n">
-        <v>364.5391937282529</v>
+        <v>365.9151892903942</v>
       </c>
       <c r="Y23" t="n">
-        <v>244.0165344526909</v>
+        <v>245.3925300148321</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>236.5778702542686</v>
+        <v>1158.550335985969</v>
       </c>
       <c r="C24" t="n">
-        <v>236.5778702542686</v>
+        <v>931.096990694248</v>
       </c>
       <c r="D24" t="n">
-        <v>236.5778702542686</v>
+        <v>579.6447817066695</v>
       </c>
       <c r="E24" t="n">
-        <v>236.5778702542686</v>
+        <v>579.6447817066695</v>
       </c>
       <c r="F24" t="n">
         <v>236.5778702542686</v>
@@ -6059,52 +6059,52 @@
         <v>31.92</v>
       </c>
       <c r="J24" t="n">
-        <v>195.3087431941669</v>
+        <v>31.92</v>
       </c>
       <c r="K24" t="n">
-        <v>451.897509099871</v>
+        <v>288.5087659057041</v>
       </c>
       <c r="L24" t="n">
-        <v>813.8701423931843</v>
+        <v>650.4813991990175</v>
       </c>
       <c r="M24" t="n">
-        <v>1005.702484136043</v>
+        <v>842.3137409418766</v>
       </c>
       <c r="N24" t="n">
-        <v>1247.53350421531</v>
+        <v>1065.426303846774</v>
       </c>
       <c r="O24" t="n">
-        <v>1403.771471379557</v>
+        <v>1403.77147137955</v>
       </c>
       <c r="P24" t="n">
-        <v>1596.000000000007</v>
+        <v>1596</v>
       </c>
       <c r="Q24" t="n">
-        <v>1475.53098818763</v>
+        <v>1475.530988187623</v>
       </c>
       <c r="R24" t="n">
-        <v>1345.128410400398</v>
+        <v>1345.12841040039</v>
       </c>
       <c r="S24" t="n">
-        <v>1277.721091968448</v>
+        <v>1277.721091968441</v>
       </c>
       <c r="T24" t="n">
-        <v>1265.944847323351</v>
+        <v>1265.944847323344</v>
       </c>
       <c r="U24" t="n">
-        <v>1078.248710871969</v>
+        <v>1257.679570645434</v>
       </c>
       <c r="V24" t="n">
-        <v>675.2184078416651</v>
+        <v>1234.941522977232</v>
       </c>
       <c r="W24" t="n">
-        <v>272.1881048113614</v>
+        <v>1194.160570543062</v>
       </c>
       <c r="X24" t="n">
-        <v>244.0439235533942</v>
+        <v>1166.016389285095</v>
       </c>
       <c r="Y24" t="n">
-        <v>236.5778702542686</v>
+        <v>1158.550335985969</v>
       </c>
     </row>
     <row r="25">
@@ -6117,25 +6117,25 @@
         <v>31.92</v>
       </c>
       <c r="C25" t="n">
-        <v>150.0020058184358</v>
+        <v>31.92</v>
       </c>
       <c r="D25" t="n">
-        <v>150.0020058184358</v>
+        <v>35.61264445680668</v>
       </c>
       <c r="E25" t="n">
-        <v>259.9109100298488</v>
+        <v>145.5215486682197</v>
       </c>
       <c r="F25" t="n">
-        <v>376.3518826217843</v>
+        <v>261.9625212601552</v>
       </c>
       <c r="G25" t="n">
-        <v>522.1883567053908</v>
+        <v>407.7989953437618</v>
       </c>
       <c r="H25" t="n">
-        <v>686.8959438320014</v>
+        <v>572.5065824703725</v>
       </c>
       <c r="I25" t="n">
-        <v>910.6315165385761</v>
+        <v>796.2421551769471</v>
       </c>
       <c r="J25" t="n">
         <v>1174.144405337595</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>372.8834581714278</v>
+        <v>538.4387456142554</v>
       </c>
       <c r="C26" t="n">
-        <v>228.9697427744642</v>
+        <v>518.6659372824197</v>
       </c>
       <c r="D26" t="n">
-        <v>124.5867571786564</v>
+        <v>414.2829516866119</v>
       </c>
       <c r="E26" t="n">
-        <v>26.24000000000117</v>
+        <v>315.9361945079567</v>
       </c>
       <c r="F26" t="n">
-        <v>26.24000000000117</v>
+        <v>217.057781671581</v>
       </c>
       <c r="G26" t="n">
-        <v>26.24000000000117</v>
+        <v>120.1189608750924</v>
       </c>
       <c r="H26" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="I26" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="J26" t="n">
-        <v>57.75406683243713</v>
+        <v>57.75406683243596</v>
       </c>
       <c r="K26" t="n">
-        <v>156.9806624103265</v>
+        <v>156.9806624103254</v>
       </c>
       <c r="L26" t="n">
-        <v>280.0800284404773</v>
+        <v>280.0800284404762</v>
       </c>
       <c r="M26" t="n">
-        <v>604.8000284404774</v>
+        <v>604.8000284404761</v>
       </c>
       <c r="N26" t="n">
-        <v>929.5200284404774</v>
+        <v>875.3905430081138</v>
       </c>
       <c r="O26" t="n">
-        <v>991.406022687754</v>
+        <v>1200.110543008114</v>
       </c>
       <c r="P26" t="n">
-        <v>1103.29547967964</v>
+        <v>1312</v>
       </c>
       <c r="Q26" t="n">
-        <v>1312.000000000058</v>
+        <v>1312</v>
       </c>
       <c r="R26" t="n">
-        <v>1312.000000000058</v>
+        <v>1312</v>
       </c>
       <c r="S26" t="n">
-        <v>1312.000000000058</v>
+        <v>1312</v>
       </c>
       <c r="T26" t="n">
-        <v>1312.000000000058</v>
+        <v>1032.983458890492</v>
       </c>
       <c r="U26" t="n">
-        <v>1312.000000000058</v>
+        <v>1032.983458890492</v>
       </c>
       <c r="V26" t="n">
-        <v>1312.000000000058</v>
+        <v>1032.983458890492</v>
       </c>
       <c r="W26" t="n">
-        <v>1044.195154231073</v>
+        <v>1032.983458890492</v>
       </c>
       <c r="X26" t="n">
-        <v>756.0316860889843</v>
+        <v>744.8199907484033</v>
       </c>
       <c r="Y26" t="n">
-        <v>549.6504409548364</v>
+        <v>538.4387456142554</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>231.0484388053447</v>
+        <v>231.0484388053435</v>
       </c>
       <c r="C27" t="n">
-        <v>176.4020625977494</v>
+        <v>176.4020625977483</v>
       </c>
       <c r="D27" t="n">
-        <v>135.0508637111811</v>
+        <v>135.0508637111799</v>
       </c>
       <c r="E27" t="n">
-        <v>99.01844227490577</v>
+        <v>99.01844227490457</v>
       </c>
       <c r="F27" t="n">
-        <v>66.052540923515</v>
+        <v>66.0525409235138</v>
       </c>
       <c r="G27" t="n">
-        <v>47.54956014637665</v>
+        <v>47.54956014637546</v>
       </c>
       <c r="H27" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="I27" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="J27" t="n">
-        <v>26.24000000000117</v>
+        <v>189.6287431941669</v>
       </c>
       <c r="K27" t="n">
-        <v>282.8287659057053</v>
+        <v>446.217509099871</v>
       </c>
       <c r="L27" t="n">
-        <v>607.5487659057053</v>
+        <v>770.937509099871</v>
       </c>
       <c r="M27" t="n">
-        <v>795.0514713796083</v>
+        <v>962.7698508427302</v>
       </c>
       <c r="N27" t="n">
-        <v>795.0514713796083</v>
+        <v>962.7698508427302</v>
       </c>
       <c r="O27" t="n">
-        <v>1119.771471379608</v>
+        <v>1119.77147137955</v>
       </c>
       <c r="P27" t="n">
-        <v>1312.000000000058</v>
+        <v>1312</v>
       </c>
       <c r="Q27" t="n">
-        <v>1312.000000000058</v>
+        <v>1312</v>
       </c>
       <c r="R27" t="n">
-        <v>1096.976570438278</v>
+        <v>1096.976570438276</v>
       </c>
       <c r="S27" t="n">
-        <v>943.710666147742</v>
+        <v>943.7106661477408</v>
       </c>
       <c r="T27" t="n">
-        <v>846.0758356440592</v>
+        <v>846.0758356440581</v>
       </c>
       <c r="U27" t="n">
-        <v>751.9519731075642</v>
+        <v>751.9519731075629</v>
       </c>
       <c r="V27" t="n">
-        <v>643.3553395807761</v>
+        <v>643.3553395807749</v>
       </c>
       <c r="W27" t="n">
-        <v>516.71580128802</v>
+        <v>516.7158012880187</v>
       </c>
       <c r="X27" t="n">
-        <v>402.7130341714669</v>
+        <v>402.7130341714657</v>
       </c>
       <c r="Y27" t="n">
-        <v>309.3883950137554</v>
+        <v>309.3883950137542</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>562.8007605089552</v>
+        <v>562.8007605089541</v>
       </c>
       <c r="C28" t="n">
-        <v>596.732766327391</v>
+        <v>596.7327663273899</v>
       </c>
       <c r="D28" t="n">
-        <v>617.981910452391</v>
+        <v>617.9819104523899</v>
       </c>
       <c r="E28" t="n">
-        <v>643.740814663804</v>
+        <v>643.7408146638029</v>
       </c>
       <c r="F28" t="n">
-        <v>676.0317872557396</v>
+        <v>676.0317872557384</v>
       </c>
       <c r="G28" t="n">
-        <v>737.7182613393461</v>
+        <v>737.718261339345</v>
       </c>
       <c r="H28" t="n">
-        <v>818.2758484659568</v>
+        <v>818.2758484659556</v>
       </c>
       <c r="I28" t="n">
-        <v>957.8614211725314</v>
+        <v>957.8614211725303</v>
       </c>
       <c r="J28" t="n">
-        <v>1251.613671333179</v>
+        <v>1251.613671333178</v>
       </c>
       <c r="K28" t="n">
-        <v>1310.561075761851</v>
+        <v>1310.56107576185</v>
       </c>
       <c r="L28" t="n">
-        <v>1245.914258116139</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="M28" t="n">
-        <v>1086.088123068026</v>
+        <v>1086.088123068025</v>
       </c>
       <c r="N28" t="n">
-        <v>1024.928883435903</v>
+        <v>873.8671992135332</v>
       </c>
       <c r="O28" t="n">
-        <v>738.5773118376264</v>
+        <v>587.5156276152568</v>
       </c>
       <c r="P28" t="n">
-        <v>738.5773118376264</v>
+        <v>587.5156276152568</v>
       </c>
       <c r="Q28" t="n">
-        <v>407.264180524495</v>
+        <v>256.202496302113</v>
       </c>
       <c r="R28" t="n">
-        <v>75.95104921136365</v>
+        <v>75.95104921136252</v>
       </c>
       <c r="S28" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="T28" t="n">
-        <v>123.740741453888</v>
+        <v>123.7407414538868</v>
       </c>
       <c r="U28" t="n">
-        <v>278.241019993814</v>
+        <v>278.2410199938129</v>
       </c>
       <c r="V28" t="n">
-        <v>384.99241287976</v>
+        <v>384.9924128797588</v>
       </c>
       <c r="W28" t="n">
-        <v>464.8133311394374</v>
+        <v>464.8133311394362</v>
       </c>
       <c r="X28" t="n">
-        <v>523.7741221636309</v>
+        <v>523.7741221636297</v>
       </c>
       <c r="Y28" t="n">
-        <v>543.1134228426631</v>
+        <v>543.113422842662</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>471.7618710078034</v>
+        <v>264.0326762720559</v>
       </c>
       <c r="C29" t="n">
-        <v>327.8481556108399</v>
+        <v>120.1189608750924</v>
       </c>
       <c r="D29" t="n">
-        <v>223.465170015032</v>
+        <v>120.1189608750924</v>
       </c>
       <c r="E29" t="n">
-        <v>125.1184128363768</v>
+        <v>120.1189608750924</v>
       </c>
       <c r="F29" t="n">
-        <v>26.24000000000117</v>
+        <v>120.1189608750924</v>
       </c>
       <c r="G29" t="n">
-        <v>26.24000000000117</v>
+        <v>120.1189608750924</v>
       </c>
       <c r="H29" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="I29" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="J29" t="n">
-        <v>57.75406683243713</v>
+        <v>57.75406683243596</v>
       </c>
       <c r="K29" t="n">
-        <v>156.9806624103265</v>
+        <v>156.9806624103254</v>
       </c>
       <c r="L29" t="n">
-        <v>280.0800284404773</v>
+        <v>280.0800284404762</v>
       </c>
       <c r="M29" t="n">
-        <v>604.8000284404783</v>
+        <v>488.7845487608354</v>
       </c>
       <c r="N29" t="n">
-        <v>813.5045487608475</v>
+        <v>813.5045487608363</v>
       </c>
       <c r="O29" t="n">
-        <v>875.390543008124</v>
+        <v>875.3905430081129</v>
       </c>
       <c r="P29" t="n">
-        <v>987.2800000000102</v>
+        <v>987.2799999999991</v>
       </c>
       <c r="Q29" t="n">
-        <v>1312.000000000011</v>
+        <v>1312</v>
       </c>
       <c r="R29" t="n">
-        <v>1312.000000000011</v>
+        <v>1312</v>
       </c>
       <c r="S29" t="n">
-        <v>1312.000000000011</v>
+        <v>1140.39091724957</v>
       </c>
       <c r="T29" t="n">
-        <v>1268.005453246456</v>
+        <v>861.3743761400617</v>
       </c>
       <c r="U29" t="n">
-        <v>936.6923219333006</v>
+        <v>728.9631271975531</v>
       </c>
       <c r="V29" t="n">
-        <v>936.6923219333006</v>
+        <v>728.9631271975531</v>
       </c>
       <c r="W29" t="n">
-        <v>936.6923219333006</v>
+        <v>728.9631271975531</v>
       </c>
       <c r="X29" t="n">
-        <v>648.528853791212</v>
+        <v>440.7996590554645</v>
       </c>
       <c r="Y29" t="n">
-        <v>648.528853791212</v>
+        <v>440.7996590554645</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>231.0484388053447</v>
+        <v>231.0484388053435</v>
       </c>
       <c r="C30" t="n">
-        <v>176.4020625977494</v>
+        <v>176.4020625977483</v>
       </c>
       <c r="D30" t="n">
-        <v>135.0508637111811</v>
+        <v>135.0508637111799</v>
       </c>
       <c r="E30" t="n">
-        <v>99.01844227490574</v>
+        <v>99.01844227490457</v>
       </c>
       <c r="F30" t="n">
-        <v>66.05254092351497</v>
+        <v>66.0525409235138</v>
       </c>
       <c r="G30" t="n">
-        <v>47.54956014637662</v>
+        <v>47.54956014637546</v>
       </c>
       <c r="H30" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="I30" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="J30" t="n">
-        <v>189.628743194168</v>
+        <v>189.6287431941669</v>
       </c>
       <c r="K30" t="n">
-        <v>446.2175090998721</v>
+        <v>446.217509099871</v>
       </c>
       <c r="L30" t="n">
-        <v>553.6166381778846</v>
+        <v>446.217509099871</v>
       </c>
       <c r="M30" t="n">
-        <v>745.4489799207438</v>
+        <v>638.0498508427302</v>
       </c>
       <c r="N30" t="n">
-        <v>987.2800000000102</v>
+        <v>879.8808709219966</v>
       </c>
       <c r="O30" t="n">
-        <v>1312.000000000011</v>
+        <v>1119.77147137955</v>
       </c>
       <c r="P30" t="n">
-        <v>1312.000000000011</v>
+        <v>1312</v>
       </c>
       <c r="Q30" t="n">
         <v>1312.000000000011</v>
       </c>
       <c r="R30" t="n">
-        <v>1095.738836354192</v>
+        <v>1096.976570438276</v>
       </c>
       <c r="S30" t="n">
-        <v>942.4729320636569</v>
+        <v>943.7106661477408</v>
       </c>
       <c r="T30" t="n">
-        <v>844.8381015599742</v>
+        <v>846.0758356440581</v>
       </c>
       <c r="U30" t="n">
-        <v>750.7142390234791</v>
+        <v>751.9519731075629</v>
       </c>
       <c r="V30" t="n">
-        <v>642.117605496691</v>
+        <v>643.3553395807749</v>
       </c>
       <c r="W30" t="n">
-        <v>516.71580128802</v>
+        <v>516.7158012880187</v>
       </c>
       <c r="X30" t="n">
-        <v>402.7130341714669</v>
+        <v>402.7130341714657</v>
       </c>
       <c r="Y30" t="n">
-        <v>309.3883950137554</v>
+        <v>309.3883950137542</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>562.8007605089552</v>
+        <v>562.8007605089541</v>
       </c>
       <c r="C31" t="n">
-        <v>596.732766327391</v>
+        <v>596.7327663273899</v>
       </c>
       <c r="D31" t="n">
-        <v>617.981910452391</v>
+        <v>617.9819104523899</v>
       </c>
       <c r="E31" t="n">
-        <v>643.740814663804</v>
+        <v>643.7408146638029</v>
       </c>
       <c r="F31" t="n">
-        <v>676.0317872557396</v>
+        <v>676.0317872557384</v>
       </c>
       <c r="G31" t="n">
-        <v>737.7182613393461</v>
+        <v>737.718261339345</v>
       </c>
       <c r="H31" t="n">
-        <v>818.2758484659568</v>
+        <v>818.2758484659556</v>
       </c>
       <c r="I31" t="n">
-        <v>957.8614211725314</v>
+        <v>957.8614211725303</v>
       </c>
       <c r="J31" t="n">
-        <v>1251.613671333179</v>
+        <v>1251.613671333178</v>
       </c>
       <c r="K31" t="n">
-        <v>1310.561075761851</v>
+        <v>1310.56107576185</v>
       </c>
       <c r="L31" t="n">
-        <v>1245.914258116139</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="M31" t="n">
-        <v>1086.088123068026</v>
+        <v>1232.400317793963</v>
       </c>
       <c r="N31" t="n">
-        <v>1069.890443150833</v>
+        <v>1020.179393939471</v>
       </c>
       <c r="O31" t="n">
-        <v>1069.890443150833</v>
+        <v>1020.179393939471</v>
       </c>
       <c r="P31" t="n">
-        <v>738.5773118376749</v>
+        <v>688.8662626263122</v>
       </c>
       <c r="Q31" t="n">
-        <v>407.2641805245146</v>
+        <v>357.5531313131514</v>
       </c>
       <c r="R31" t="n">
-        <v>75.95104921136368</v>
+        <v>26.24</v>
       </c>
       <c r="S31" t="n">
-        <v>26.24000000000117</v>
+        <v>26.24</v>
       </c>
       <c r="T31" t="n">
-        <v>123.740741453888</v>
+        <v>123.7407414538868</v>
       </c>
       <c r="U31" t="n">
-        <v>278.241019993814</v>
+        <v>278.2410199938129</v>
       </c>
       <c r="V31" t="n">
-        <v>384.99241287976</v>
+        <v>384.9924128797588</v>
       </c>
       <c r="W31" t="n">
-        <v>464.8133311394374</v>
+        <v>464.8133311394362</v>
       </c>
       <c r="X31" t="n">
-        <v>523.7741221636309</v>
+        <v>523.7741221636297</v>
       </c>
       <c r="Y31" t="n">
-        <v>543.1134228426631</v>
+        <v>543.113422842662</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="C32" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="D32" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="E32" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="F32" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="G32" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="H32" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="I32" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="J32" t="n">
-        <v>46.71406683243713</v>
+        <v>46.71406683243596</v>
       </c>
       <c r="K32" t="n">
-        <v>145.9406624103266</v>
+        <v>145.9406624103254</v>
       </c>
       <c r="L32" t="n">
-        <v>269.0400284404773</v>
+        <v>269.0400284404761</v>
       </c>
       <c r="M32" t="n">
-        <v>457.1400284404804</v>
+        <v>269.0400284404762</v>
       </c>
       <c r="N32" t="n">
-        <v>586.2245487608957</v>
+        <v>398.1245487608342</v>
       </c>
       <c r="O32" t="n">
-        <v>648.1105430081723</v>
+        <v>460.0105430081108</v>
       </c>
       <c r="P32" t="n">
-        <v>760.0000000000584</v>
+        <v>571.899999999997</v>
       </c>
       <c r="Q32" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="R32" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="S32" t="n">
-        <v>747.9868768455877</v>
+        <v>747.9868768455293</v>
       </c>
       <c r="T32" t="n">
-        <v>628.5662953320391</v>
+        <v>628.5662953319807</v>
       </c>
       <c r="U32" t="n">
-        <v>549.3647265119406</v>
+        <v>442.5478495009389</v>
       </c>
       <c r="V32" t="n">
-        <v>382.8485404848458</v>
+        <v>276.0316634738441</v>
       </c>
       <c r="W32" t="n">
-        <v>207.7238172717674</v>
+        <v>100.9069402607658</v>
       </c>
       <c r="X32" t="n">
-        <v>79.15630872563844</v>
+        <v>15.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>32.37102318745017</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>207.1191919191962</v>
+        <v>15.2</v>
       </c>
       <c r="C33" t="n">
-        <v>207.1191919191962</v>
+        <v>15.2</v>
       </c>
       <c r="D33" t="n">
-        <v>207.1191919191962</v>
+        <v>15.2</v>
       </c>
       <c r="E33" t="n">
-        <v>207.1191919191962</v>
+        <v>15.2</v>
       </c>
       <c r="F33" t="n">
-        <v>207.1191919191962</v>
+        <v>15.2</v>
       </c>
       <c r="G33" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="H33" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="I33" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="J33" t="n">
-        <v>178.588743194168</v>
+        <v>178.5887431941669</v>
       </c>
       <c r="K33" t="n">
-        <v>178.588743194168</v>
+        <v>366.6887431941699</v>
       </c>
       <c r="L33" t="n">
-        <v>178.588743194168</v>
+        <v>383.799999999994</v>
       </c>
       <c r="M33" t="n">
-        <v>195.7000000000495</v>
+        <v>571.899999999997</v>
       </c>
       <c r="N33" t="n">
-        <v>383.8000000000525</v>
+        <v>760</v>
       </c>
       <c r="O33" t="n">
-        <v>571.9000000000555</v>
+        <v>760</v>
       </c>
       <c r="P33" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="Q33" t="n">
-        <v>639.5309881876815</v>
+        <v>639.5309881876231</v>
       </c>
       <c r="R33" t="n">
-        <v>447.6117962684865</v>
+        <v>447.6117962684281</v>
       </c>
       <c r="S33" t="n">
-        <v>399.0383838383912</v>
+        <v>255.6926043492331</v>
       </c>
       <c r="T33" t="n">
-        <v>399.0383838383912</v>
+        <v>63.77341243003804</v>
       </c>
       <c r="U33" t="n">
-        <v>399.0383838383912</v>
+        <v>15.2</v>
       </c>
       <c r="V33" t="n">
-        <v>399.0383838383912</v>
+        <v>15.2</v>
       </c>
       <c r="W33" t="n">
-        <v>399.0383838383912</v>
+        <v>15.2</v>
       </c>
       <c r="X33" t="n">
-        <v>207.1191919191962</v>
+        <v>15.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>207.1191919191962</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>191.3073376662933</v>
+        <v>571.899999999997</v>
       </c>
       <c r="C34" t="n">
-        <v>206.1308558750524</v>
+        <v>571.899999999997</v>
       </c>
       <c r="D34" t="n">
-        <v>383.8000000000525</v>
+        <v>571.899999999997</v>
       </c>
       <c r="E34" t="n">
-        <v>383.8000000000525</v>
+        <v>571.899999999997</v>
       </c>
       <c r="F34" t="n">
-        <v>571.9000000000555</v>
+        <v>760</v>
       </c>
       <c r="G34" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="H34" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="I34" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="J34" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="K34" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="L34" t="n">
-        <v>760.0000000000584</v>
+        <v>760</v>
       </c>
       <c r="M34" t="n">
-        <v>759.769824547905</v>
+        <v>759.7698245478466</v>
       </c>
       <c r="N34" t="n">
-        <v>707.1448602893726</v>
+        <v>707.1448602893141</v>
       </c>
       <c r="O34" t="n">
-        <v>580.3892482870557</v>
+        <v>580.3892482869973</v>
       </c>
       <c r="P34" t="n">
-        <v>398.8734718832649</v>
+        <v>398.8734718832065</v>
       </c>
       <c r="Q34" t="n">
-        <v>207.1191919192491</v>
+        <v>207.1191919192516</v>
       </c>
       <c r="R34" t="n">
-        <v>15.20000000000117</v>
+        <v>15.2</v>
       </c>
       <c r="S34" t="n">
-        <v>15.20000000000117</v>
+        <v>122.8982006679436</v>
       </c>
       <c r="T34" t="n">
-        <v>15.20000000000117</v>
+        <v>122.8982006679436</v>
       </c>
       <c r="U34" t="n">
-        <v>15.20000000000117</v>
+        <v>122.8982006679436</v>
       </c>
       <c r="V34" t="n">
-        <v>15.20000000000117</v>
+        <v>310.9982006679467</v>
       </c>
       <c r="W34" t="n">
-        <v>15.20000000000117</v>
+        <v>383.799999999994</v>
       </c>
       <c r="X34" t="n">
-        <v>15.20000000000117</v>
+        <v>571.899999999997</v>
       </c>
       <c r="Y34" t="n">
-        <v>15.20000000000117</v>
+        <v>571.899999999997</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="C35" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="D35" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="E35" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="F35" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="G35" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="H35" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="I35" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="J35" t="n">
-        <v>41.83406683243713</v>
+        <v>41.83406683243596</v>
       </c>
       <c r="K35" t="n">
-        <v>141.0606624103266</v>
+        <v>141.0606624103254</v>
       </c>
       <c r="L35" t="n">
-        <v>264.1600284404773</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="M35" t="n">
-        <v>264.1600284404773</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="N35" t="n">
-        <v>264.1600284404773</v>
+        <v>342.2245487608371</v>
       </c>
       <c r="O35" t="n">
-        <v>326.046022687754</v>
+        <v>404.1105430081138</v>
       </c>
       <c r="P35" t="n">
-        <v>437.9354796796402</v>
+        <v>516</v>
       </c>
       <c r="Q35" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="R35" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="S35" t="n">
-        <v>503.9868768455878</v>
+        <v>503.9868768455294</v>
       </c>
       <c r="T35" t="n">
-        <v>384.5662953320392</v>
+        <v>503.9868768455294</v>
       </c>
       <c r="U35" t="n">
-        <v>254.2632650289355</v>
+        <v>463.4498778779696</v>
       </c>
       <c r="V35" t="n">
-        <v>204.5793390287303</v>
+        <v>333.1468475748655</v>
       </c>
       <c r="W35" t="n">
-        <v>74.27630872563844</v>
+        <v>202.8438172717663</v>
       </c>
       <c r="X35" t="n">
-        <v>74.27630872563844</v>
+        <v>74.27630872563728</v>
       </c>
       <c r="Y35" t="n">
-        <v>27.49102318745017</v>
+        <v>27.491023187449</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="C36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="D36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="E36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="F36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="G36" t="n">
-        <v>10.32000000000117</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="H36" t="n">
-        <v>10.32000000000117</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="I36" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="J36" t="n">
-        <v>138.0300000000066</v>
+        <v>138.0300000000054</v>
       </c>
       <c r="K36" t="n">
-        <v>265.740000000012</v>
+        <v>138.0300000000054</v>
       </c>
       <c r="L36" t="n">
-        <v>393.4500000000174</v>
+        <v>260.5799999999891</v>
       </c>
       <c r="M36" t="n">
-        <v>516.0000000000584</v>
+        <v>388.2899999999946</v>
       </c>
       <c r="N36" t="n">
-        <v>516.0000000000584</v>
+        <v>388.2899999999946</v>
       </c>
       <c r="O36" t="n">
-        <v>516.0000000000584</v>
+        <v>388.2899999999946</v>
       </c>
       <c r="P36" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="Q36" t="n">
-        <v>395.5309881876815</v>
+        <v>395.5309881876231</v>
       </c>
       <c r="R36" t="n">
-        <v>265.2279578846457</v>
+        <v>270.9260606060717</v>
       </c>
       <c r="S36" t="n">
-        <v>265.2279578846457</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="T36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="U36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="V36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="W36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="X36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
       <c r="Y36" t="n">
-        <v>140.623030303037</v>
+        <v>140.6230303030358</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>138.0300000000066</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="C37" t="n">
-        <v>138.0300000000066</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="D37" t="n">
-        <v>138.0300000000066</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="E37" t="n">
-        <v>265.740000000012</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="F37" t="n">
-        <v>265.740000000012</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="G37" t="n">
-        <v>393.4500000000174</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="H37" t="n">
-        <v>393.4500000000174</v>
+        <v>167.5203459745511</v>
       </c>
       <c r="I37" t="n">
-        <v>393.4500000000174</v>
+        <v>295.2303459745565</v>
       </c>
       <c r="J37" t="n">
-        <v>393.4500000000174</v>
+        <v>295.2303459745565</v>
       </c>
       <c r="K37" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="L37" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="M37" t="n">
-        <v>516.0000000000584</v>
+        <v>515.7698245478466</v>
       </c>
       <c r="N37" t="n">
-        <v>463.3750357415259</v>
+        <v>463.1448602893141</v>
       </c>
       <c r="O37" t="n">
-        <v>336.6194237392091</v>
+        <v>336.3892482869973</v>
       </c>
       <c r="P37" t="n">
-        <v>270.9260606062072</v>
+        <v>206.086217983878</v>
       </c>
       <c r="Q37" t="n">
-        <v>140.6230303031029</v>
+        <v>140.6230303031128</v>
       </c>
       <c r="R37" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="S37" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="T37" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="U37" t="n">
-        <v>138.0300000000066</v>
+        <v>10.32</v>
       </c>
       <c r="V37" t="n">
-        <v>138.0300000000066</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="W37" t="n">
-        <v>138.0300000000066</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="X37" t="n">
-        <v>138.0300000000066</v>
+        <v>39.81034597454568</v>
       </c>
       <c r="Y37" t="n">
-        <v>138.0300000000066</v>
+        <v>39.81034597454568</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="C38" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="D38" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="E38" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="F38" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="G38" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="H38" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="I38" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="J38" t="n">
-        <v>41.83406683243713</v>
+        <v>41.83406683243596</v>
       </c>
       <c r="K38" t="n">
-        <v>141.0606624103266</v>
+        <v>141.0606624103254</v>
       </c>
       <c r="L38" t="n">
-        <v>264.1600284404773</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="M38" t="n">
-        <v>264.1600284404773</v>
+        <v>342.2245487608371</v>
       </c>
       <c r="N38" t="n">
-        <v>342.2245487608956</v>
+        <v>342.2245487608371</v>
       </c>
       <c r="O38" t="n">
-        <v>404.1105430081722</v>
+        <v>404.1105430081138</v>
       </c>
       <c r="P38" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="Q38" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="R38" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="S38" t="n">
-        <v>503.9868768455878</v>
+        <v>503.9868768455294</v>
       </c>
       <c r="T38" t="n">
-        <v>384.5662953320392</v>
+        <v>384.5662953319808</v>
       </c>
       <c r="U38" t="n">
-        <v>254.2632650289094</v>
+        <v>333.146847574891</v>
       </c>
       <c r="V38" t="n">
-        <v>123.9602347258048</v>
+        <v>333.146847574891</v>
       </c>
       <c r="W38" t="n">
-        <v>10.32000000000117</v>
+        <v>202.8438172717663</v>
       </c>
       <c r="X38" t="n">
-        <v>10.32000000000117</v>
+        <v>74.27630872563728</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.32000000000117</v>
+        <v>27.491023187449</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>270.9260606060802</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="C39" t="n">
-        <v>270.9260606060802</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="D39" t="n">
-        <v>140.6230303030407</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="E39" t="n">
-        <v>140.6230303030407</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="F39" t="n">
-        <v>140.6230303030407</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="G39" t="n">
-        <v>140.6230303030407</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="H39" t="n">
-        <v>140.6230303030407</v>
+        <v>10.32</v>
       </c>
       <c r="I39" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="J39" t="n">
-        <v>10.32000000000117</v>
+        <v>132.8699999999729</v>
       </c>
       <c r="K39" t="n">
-        <v>10.32000000000117</v>
+        <v>132.8699999999729</v>
       </c>
       <c r="L39" t="n">
-        <v>138.0300000000102</v>
+        <v>132.8699999999729</v>
       </c>
       <c r="M39" t="n">
-        <v>265.7400000000192</v>
+        <v>260.579999999982</v>
       </c>
       <c r="N39" t="n">
-        <v>393.4500000000282</v>
+        <v>260.579999999982</v>
       </c>
       <c r="O39" t="n">
-        <v>516.0000000000584</v>
+        <v>388.289999999991</v>
       </c>
       <c r="P39" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="Q39" t="n">
-        <v>395.5309881876815</v>
+        <v>395.5309881876231</v>
       </c>
       <c r="R39" t="n">
-        <v>338.8657841378225</v>
+        <v>338.865784137764</v>
       </c>
       <c r="S39" t="n">
-        <v>270.9260606060802</v>
+        <v>338.865784137764</v>
       </c>
       <c r="T39" t="n">
-        <v>270.9260606060802</v>
+        <v>338.865784137764</v>
       </c>
       <c r="U39" t="n">
-        <v>270.9260606060802</v>
+        <v>338.865784137764</v>
       </c>
       <c r="V39" t="n">
-        <v>270.9260606060802</v>
+        <v>208.5627538347245</v>
       </c>
       <c r="W39" t="n">
-        <v>270.9260606060802</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="X39" t="n">
-        <v>270.9260606060802</v>
+        <v>78.25972353168498</v>
       </c>
       <c r="Y39" t="n">
-        <v>270.9260606060802</v>
+        <v>78.25972353168498</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>516.0000000000584</v>
+        <v>245.7282006679526</v>
       </c>
       <c r="C40" t="n">
-        <v>516.0000000000584</v>
+        <v>373.4382006679617</v>
       </c>
       <c r="D40" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="E40" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="F40" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="G40" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="H40" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="I40" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="J40" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="K40" t="n">
-        <v>516.0000000000584</v>
+        <v>422.940345974562</v>
       </c>
       <c r="L40" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="M40" t="n">
-        <v>515.769824547905</v>
+        <v>515.7698245478466</v>
       </c>
       <c r="N40" t="n">
-        <v>515.769824547905</v>
+        <v>463.1448602893141</v>
       </c>
       <c r="O40" t="n">
-        <v>401.2290909094083</v>
+        <v>336.3892482869973</v>
       </c>
       <c r="P40" t="n">
-        <v>270.9260606062667</v>
+        <v>206.0862179838483</v>
       </c>
       <c r="Q40" t="n">
-        <v>140.6230303031289</v>
+        <v>75.78318768069951</v>
       </c>
       <c r="R40" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="S40" t="n">
-        <v>10.32000000000117</v>
+        <v>118.0182006679436</v>
       </c>
       <c r="T40" t="n">
-        <v>138.0300000000102</v>
+        <v>245.7282006679526</v>
       </c>
       <c r="U40" t="n">
-        <v>138.0300000000102</v>
+        <v>245.7282006679526</v>
       </c>
       <c r="V40" t="n">
-        <v>138.0300000000102</v>
+        <v>245.7282006679526</v>
       </c>
       <c r="W40" t="n">
-        <v>265.7400000000192</v>
+        <v>245.7282006679526</v>
       </c>
       <c r="X40" t="n">
-        <v>393.4500000000282</v>
+        <v>245.7282006679526</v>
       </c>
       <c r="Y40" t="n">
-        <v>516.0000000000584</v>
+        <v>245.7282006679526</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>125.0909090905245</v>
+        <v>140.6230303030469</v>
       </c>
       <c r="C41" t="n">
-        <v>125.0909090905245</v>
+        <v>140.6230303030469</v>
       </c>
       <c r="D41" t="n">
-        <v>125.0909090905245</v>
+        <v>140.6230303030469</v>
       </c>
       <c r="E41" t="n">
-        <v>125.0909090905245</v>
+        <v>10.32</v>
       </c>
       <c r="F41" t="n">
-        <v>125.0909090905245</v>
+        <v>10.32</v>
       </c>
       <c r="G41" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="H41" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="I41" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="J41" t="n">
-        <v>41.83406683243713</v>
+        <v>41.83406683243596</v>
       </c>
       <c r="K41" t="n">
-        <v>141.0606624103266</v>
+        <v>141.0606624103254</v>
       </c>
       <c r="L41" t="n">
-        <v>264.1600284404773</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="M41" t="n">
-        <v>264.1600284404773</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="N41" t="n">
-        <v>342.2245487608956</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="O41" t="n">
-        <v>404.1105430081722</v>
+        <v>326.0460226877527</v>
       </c>
       <c r="P41" t="n">
-        <v>516.0000000000584</v>
+        <v>437.9354796796389</v>
       </c>
       <c r="Q41" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="R41" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="S41" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="T41" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="U41" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="V41" t="n">
-        <v>385.6969696968859</v>
+        <v>516</v>
       </c>
       <c r="W41" t="n">
-        <v>255.393939393704</v>
+        <v>516</v>
       </c>
       <c r="X41" t="n">
-        <v>255.393939393704</v>
+        <v>401.2290909091406</v>
       </c>
       <c r="Y41" t="n">
-        <v>125.0909090905245</v>
+        <v>270.9260606060938</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>105.9121639776546</v>
+        <v>105.9121639776534</v>
       </c>
       <c r="C42" t="n">
-        <v>105.9121639776546</v>
+        <v>105.9121639776534</v>
       </c>
       <c r="D42" t="n">
-        <v>105.9121639776546</v>
+        <v>105.9121639776534</v>
       </c>
       <c r="E42" t="n">
-        <v>105.9121639776546</v>
+        <v>105.9121639776534</v>
       </c>
       <c r="F42" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="G42" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="H42" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="I42" t="n">
-        <v>10.32000000000117</v>
+        <v>10.32</v>
       </c>
       <c r="J42" t="n">
-        <v>10.32000000000117</v>
+        <v>138.0300000000162</v>
       </c>
       <c r="K42" t="n">
-        <v>10.32000000000117</v>
+        <v>138.0300000000162</v>
       </c>
       <c r="L42" t="n">
-        <v>10.32000000000117</v>
+        <v>265.7400000000325</v>
       </c>
       <c r="M42" t="n">
-        <v>138.0300000000174</v>
+        <v>388.2899999999838</v>
       </c>
       <c r="N42" t="n">
-        <v>265.7400000000337</v>
+        <v>388.2899999999838</v>
       </c>
       <c r="O42" t="n">
-        <v>388.2900000000422</v>
+        <v>516</v>
       </c>
       <c r="P42" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="Q42" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="R42" t="n">
-        <v>516.0000000000584</v>
+        <v>516</v>
       </c>
       <c r="S42" t="n">
-        <v>385.6969696968498</v>
+        <v>516</v>
       </c>
       <c r="T42" t="n">
-        <v>385.6969696968498</v>
+        <v>516</v>
       </c>
       <c r="U42" t="n">
-        <v>366.5182245840065</v>
+        <v>516</v>
       </c>
       <c r="V42" t="n">
-        <v>236.2151942808331</v>
+        <v>385.6969696968118</v>
       </c>
       <c r="W42" t="n">
-        <v>105.9121639776546</v>
+        <v>255.3939393936186</v>
       </c>
       <c r="X42" t="n">
-        <v>105.9121639776546</v>
+        <v>125.0909090904305</v>
       </c>
       <c r="Y42" t="n">
-        <v>105.9121639776546</v>
+        <v>105.9121639776534</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>200.905002422157</v>
+        <v>145.2949752609077</v>
       </c>
       <c r="C43" t="n">
-        <v>172.8997027776674</v>
+        <v>117.2896756164182</v>
       </c>
       <c r="D43" t="n">
-        <v>131.954027974076</v>
+        <v>76.34400081282675</v>
       </c>
       <c r="E43" t="n">
-        <v>95.60967965391791</v>
+        <v>39.99965249266862</v>
       </c>
       <c r="F43" t="n">
-        <v>65.93002716124928</v>
+        <v>10.32</v>
       </c>
       <c r="G43" t="n">
-        <v>66.23650124485586</v>
+        <v>10.62647408360658</v>
       </c>
       <c r="H43" t="n">
-        <v>85.41408837146653</v>
+        <v>29.80406121021726</v>
       </c>
       <c r="I43" t="n">
-        <v>163.6196610780412</v>
+        <v>108.009633916792</v>
       </c>
       <c r="J43" t="n">
-        <v>291.3296610780575</v>
+        <v>235.7196339168082</v>
       </c>
       <c r="K43" t="n">
-        <v>288.8476739631423</v>
+        <v>235.7196339168082</v>
       </c>
       <c r="L43" t="n">
-        <v>161.574593691168</v>
+        <v>235.7196339168082</v>
       </c>
       <c r="M43" t="n">
-        <v>140.6230303032227</v>
+        <v>235.7196339168082</v>
       </c>
       <c r="N43" t="n">
-        <v>140.6230303032227</v>
+        <v>235.7196339168082</v>
       </c>
       <c r="O43" t="n">
-        <v>140.6230303032227</v>
+        <v>235.7196339168082</v>
       </c>
       <c r="P43" t="n">
-        <v>10.32000000000117</v>
+        <v>235.7196339168082</v>
       </c>
       <c r="Q43" t="n">
-        <v>10.32000000000117</v>
+        <v>235.7196339168082</v>
       </c>
       <c r="R43" t="n">
-        <v>10.32000000000117</v>
+        <v>152.4807727435902</v>
       </c>
       <c r="S43" t="n">
-        <v>10.32000000000117</v>
+        <v>40.14346090596504</v>
       </c>
       <c r="T43" t="n">
-        <v>46.44074145388799</v>
+        <v>76.26420235985186</v>
       </c>
       <c r="U43" t="n">
-        <v>139.561019993814</v>
+        <v>169.3844808997779</v>
       </c>
       <c r="V43" t="n">
-        <v>184.93241287976</v>
+        <v>214.7558737857238</v>
       </c>
       <c r="W43" t="n">
-        <v>203.3733311394374</v>
+        <v>233.1967920454012</v>
       </c>
       <c r="X43" t="n">
-        <v>200.905002422157</v>
+        <v>230.7284633281209</v>
       </c>
       <c r="Y43" t="n">
-        <v>200.905002422157</v>
+        <v>187.8341675205832</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>136.2626262626633</v>
+        <v>388.7878787879864</v>
       </c>
       <c r="C44" t="n">
-        <v>136.2626262626633</v>
+        <v>388.7878787879864</v>
       </c>
       <c r="D44" t="n">
-        <v>136.2626262626633</v>
+        <v>388.7878787879864</v>
       </c>
       <c r="E44" t="n">
-        <v>136.2626262626633</v>
+        <v>262.5252525253243</v>
       </c>
       <c r="F44" t="n">
-        <v>136.2626262626633</v>
+        <v>136.2626262626621</v>
       </c>
       <c r="G44" t="n">
-        <v>136.2626262626633</v>
+        <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>10.00000000000117</v>
+        <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>10.00000000000117</v>
+        <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>41.51406683243712</v>
+        <v>41.51406683243596</v>
       </c>
       <c r="K44" t="n">
-        <v>140.7406624103265</v>
+        <v>140.7406624103254</v>
       </c>
       <c r="L44" t="n">
-        <v>263.8400284404773</v>
+        <v>263.8400284404761</v>
       </c>
       <c r="M44" t="n">
-        <v>263.8400284404773</v>
+        <v>263.8400284404761</v>
       </c>
       <c r="N44" t="n">
-        <v>326.2245487609973</v>
+        <v>326.2245487608371</v>
       </c>
       <c r="O44" t="n">
-        <v>388.110543008274</v>
+        <v>388.1105430081138</v>
       </c>
       <c r="P44" t="n">
-        <v>500.0000000001602</v>
+        <v>500</v>
       </c>
       <c r="Q44" t="n">
-        <v>500.0000000001602</v>
+        <v>500</v>
       </c>
       <c r="R44" t="n">
-        <v>500.0000000001602</v>
+        <v>500</v>
       </c>
       <c r="S44" t="n">
-        <v>500.0000000001602</v>
+        <v>500</v>
       </c>
       <c r="T44" t="n">
-        <v>500.0000000001602</v>
+        <v>500</v>
       </c>
       <c r="U44" t="n">
-        <v>500.0000000001602</v>
+        <v>500</v>
       </c>
       <c r="V44" t="n">
-        <v>373.737373737498</v>
+        <v>388.7878787879864</v>
       </c>
       <c r="W44" t="n">
-        <v>247.4747474748359</v>
+        <v>388.7878787879864</v>
       </c>
       <c r="X44" t="n">
-        <v>136.2626262626633</v>
+        <v>388.7878787879864</v>
       </c>
       <c r="Y44" t="n">
-        <v>136.2626262626633</v>
+        <v>388.7878787879864</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>500.0000000000584</v>
+        <v>121.2121212111099</v>
       </c>
       <c r="C45" t="n">
-        <v>382.7273611662006</v>
+        <v>121.2121212111099</v>
       </c>
       <c r="D45" t="n">
-        <v>278.7498996533697</v>
+        <v>17.23465969827899</v>
       </c>
       <c r="E45" t="n">
-        <v>189.5279867502927</v>
+        <v>17.23465969827899</v>
       </c>
       <c r="F45" t="n">
-        <v>93.93582277263926</v>
+        <v>17.23465969827899</v>
       </c>
       <c r="G45" t="n">
-        <v>93.93582277263926</v>
+        <v>17.23465969827899</v>
       </c>
       <c r="H45" t="n">
-        <v>10.00000000000117</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>10.00000000000117</v>
+        <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>10.00000000000117</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>10.00000000000117</v>
+        <v>133.7500000000351</v>
       </c>
       <c r="L45" t="n">
-        <v>133.7500000000363</v>
+        <v>133.7500000000351</v>
       </c>
       <c r="M45" t="n">
-        <v>133.7500000000363</v>
+        <v>257.5000000000351</v>
       </c>
       <c r="N45" t="n">
-        <v>252.4999999999882</v>
+        <v>376.2499999999649</v>
       </c>
       <c r="O45" t="n">
-        <v>376.2500000000233</v>
+        <v>376.2499999999649</v>
       </c>
       <c r="P45" t="n">
-        <v>500.0000000000584</v>
+        <v>500</v>
       </c>
       <c r="Q45" t="n">
-        <v>500.0000000000584</v>
+        <v>500</v>
       </c>
       <c r="R45" t="n">
-        <v>500.0000000000584</v>
+        <v>500</v>
       </c>
       <c r="S45" t="n">
-        <v>500.0000000000584</v>
+        <v>500</v>
       </c>
       <c r="T45" t="n">
-        <v>500.0000000000584</v>
+        <v>373.7373737370332</v>
       </c>
       <c r="U45" t="n">
-        <v>500.0000000000584</v>
+        <v>247.474747474052</v>
       </c>
       <c r="V45" t="n">
-        <v>500.0000000000584</v>
+        <v>247.474747474052</v>
       </c>
       <c r="W45" t="n">
-        <v>500.0000000000584</v>
+        <v>247.474747474052</v>
       </c>
       <c r="X45" t="n">
-        <v>500.0000000000584</v>
+        <v>247.474747474052</v>
       </c>
       <c r="Y45" t="n">
-        <v>500.0000000000584</v>
+        <v>121.2121212111099</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>117.6198430722242</v>
+        <v>160.5141388797608</v>
       </c>
       <c r="C46" t="n">
-        <v>89.61454342773466</v>
+        <v>160.5141388797608</v>
       </c>
       <c r="D46" t="n">
-        <v>89.61454342773466</v>
+        <v>160.5141388797608</v>
       </c>
       <c r="E46" t="n">
-        <v>89.61454342773466</v>
+        <v>160.5141388797608</v>
       </c>
       <c r="F46" t="n">
-        <v>59.93489093506604</v>
+        <v>160.5141388797608</v>
       </c>
       <c r="G46" t="n">
-        <v>60.24136501867262</v>
+        <v>160.8206129633673</v>
       </c>
       <c r="H46" t="n">
-        <v>79.4189521452833</v>
+        <v>179.998200089978</v>
       </c>
       <c r="I46" t="n">
-        <v>157.624524851858</v>
+        <v>258.2037727965527</v>
       </c>
       <c r="J46" t="n">
-        <v>281.3745248518932</v>
+        <v>381.9537727965527</v>
       </c>
       <c r="K46" t="n">
-        <v>281.3745248518932</v>
+        <v>381.9537727965527</v>
       </c>
       <c r="L46" t="n">
-        <v>281.3745248518932</v>
+        <v>255.6911465339264</v>
       </c>
       <c r="M46" t="n">
-        <v>248.5999381002885</v>
+        <v>255.6911465339264</v>
       </c>
       <c r="N46" t="n">
-        <v>248.5999381002885</v>
+        <v>255.6911465339264</v>
       </c>
       <c r="O46" t="n">
-        <v>122.3373118376263</v>
+        <v>255.6911465339264</v>
       </c>
       <c r="P46" t="n">
-        <v>122.3373118376263</v>
+        <v>248.5999381002514</v>
       </c>
       <c r="Q46" t="n">
-        <v>122.3373118376263</v>
+        <v>122.3373118376251</v>
       </c>
       <c r="R46" t="n">
-        <v>122.3373118376263</v>
+        <v>122.3373118376251</v>
       </c>
       <c r="S46" t="n">
-        <v>10.00000000000117</v>
+        <v>10</v>
       </c>
       <c r="T46" t="n">
-        <v>46.120741453888</v>
+        <v>46.12074145388683</v>
       </c>
       <c r="U46" t="n">
-        <v>139.241019993814</v>
+        <v>139.2410199938128</v>
       </c>
       <c r="V46" t="n">
-        <v>184.61241287976</v>
+        <v>184.6124128797588</v>
       </c>
       <c r="W46" t="n">
-        <v>203.0533311394374</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="X46" t="n">
-        <v>203.0533311394374</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="Y46" t="n">
-        <v>160.1590353318996</v>
+        <v>203.0533311394362</v>
       </c>
     </row>
   </sheetData>
@@ -8043,25 +8043,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>186.4256073882259</v>
+        <v>62.42560738822591</v>
       </c>
       <c r="K3" t="n">
         <v>160.6996692410901</v>
       </c>
       <c r="L3" t="n">
-        <v>22.46041394129978</v>
+        <v>146.4604139412998</v>
       </c>
       <c r="M3" t="n">
         <v>401.9247782656032</v>
       </c>
       <c r="N3" t="n">
-        <v>360.1246685054247</v>
+        <v>241.1347695155256</v>
       </c>
       <c r="O3" t="n">
         <v>40.91900331325166</v>
       </c>
       <c r="P3" t="n">
-        <v>24.9804809108019</v>
+        <v>143.9703799007009</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8213,16 +8213,16 @@
         <v>405.9068110594027</v>
       </c>
       <c r="N5" t="n">
-        <v>336.654907818579</v>
+        <v>385.0724263462538</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>10.98034647284221</v>
       </c>
       <c r="Q5" t="n">
-        <v>147.1319262124245</v>
+        <v>87.73406121190752</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8280,7 +8280,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J6" t="n">
-        <v>181.4155063781249</v>
+        <v>186.4256073882259</v>
       </c>
       <c r="K6" t="n">
         <v>36.69966924109012</v>
@@ -8295,10 +8295,10 @@
         <v>365.1347695155256</v>
       </c>
       <c r="O6" t="n">
-        <v>40.91900331325166</v>
+        <v>159.9089023031507</v>
       </c>
       <c r="P6" t="n">
-        <v>148.9804809108019</v>
+        <v>24.9804809108019</v>
       </c>
       <c r="Q6" t="n">
         <v>17.27519534353338</v>
@@ -8447,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>489.3457204739089</v>
+        <v>668.9068110594028</v>
       </c>
       <c r="N8" t="n">
         <v>599.654907818579</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>350.7340612119075</v>
+        <v>171.1729706264136</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8517,13 +8517,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J9" t="n">
-        <v>62.42560738822591</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L9" t="n">
-        <v>103.6097798727849</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M9" t="n">
         <v>471.6948204301074</v>
@@ -8532,7 +8532,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O9" t="n">
-        <v>303.9190033132517</v>
+        <v>220.0292347051744</v>
       </c>
       <c r="P9" t="n">
         <v>24.9804809108019</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>292.1676092601657</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>223.7711155778894</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>405.9068110594027</v>
+        <v>729.9068110594028</v>
       </c>
       <c r="N11" t="n">
-        <v>571.461561508273</v>
+        <v>639.8580551905492</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>411.7340612119075</v>
+        <v>87.73406121190752</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8763,13 +8763,13 @@
         <v>346.4604139412998</v>
       </c>
       <c r="M12" t="n">
-        <v>277.9247782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N12" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O12" t="n">
-        <v>331.334630405032</v>
+        <v>137.5645882405278</v>
       </c>
       <c r="P12" t="n">
         <v>24.9804809108019</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>292.1676092601657</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -8921,7 +8921,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>640.7134647490968</v>
+        <v>729.9068110594028</v>
       </c>
       <c r="N14" t="n">
         <v>660.654907818579</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>87.73406121190752</v>
+        <v>290.7083241617672</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>292.1676092601657</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -9158,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>405.9068110594027</v>
+        <v>729.9068110594028</v>
       </c>
       <c r="N17" t="n">
-        <v>571.461561508273</v>
+        <v>539.6291707684387</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9231,10 +9231,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K18" t="n">
-        <v>295.8802408630135</v>
+        <v>36.69966924109012</v>
       </c>
       <c r="L18" t="n">
-        <v>22.46041394129978</v>
+        <v>346.4604139412998</v>
       </c>
       <c r="M18" t="n">
         <v>471.6948204301074</v>
@@ -9243,10 +9243,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>267.3943573107802</v>
+        <v>364.9190033132517</v>
       </c>
       <c r="P18" t="n">
-        <v>219.1507118405495</v>
+        <v>56.8066374600014</v>
       </c>
       <c r="Q18" t="n">
         <v>17.27519534353338</v>
@@ -9389,16 +9389,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>227.7711155778894</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>733.9068110594028</v>
+        <v>733.9068110594033</v>
       </c>
       <c r="N20" t="n">
-        <v>547.4675546068225</v>
+        <v>647.6964390289326</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>415.7340612119075</v>
+        <v>87.73406121190752</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9471,19 +9471,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L21" t="n">
-        <v>22.46041394129978</v>
+        <v>181.0479094330369</v>
       </c>
       <c r="M21" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N21" t="n">
-        <v>485.4085271713503</v>
+        <v>241.1347695155256</v>
       </c>
       <c r="O21" t="n">
         <v>368.9190033132517</v>
       </c>
       <c r="P21" t="n">
-        <v>133.4644496764619</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q21" t="n">
         <v>17.27519534353338</v>
@@ -9626,13 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>298.7711155778894</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>755.8507709789653</v>
+        <v>804.9068110594035</v>
       </c>
       <c r="N23" t="n">
         <v>735.6549078185797</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>486.7340612119082</v>
+        <v>138.9069055535733</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9702,7 +9702,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J24" t="n">
-        <v>227.4647419277884</v>
+        <v>62.42560738822591</v>
       </c>
       <c r="K24" t="n">
         <v>295.8802408630135</v>
@@ -9714,10 +9714,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N24" t="n">
-        <v>485.4085271713503</v>
+        <v>466.5009946719879</v>
       </c>
       <c r="O24" t="n">
-        <v>198.7351317619863</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P24" t="n">
         <v>219.1507118405495</v>
@@ -9872,16 +9872,16 @@
         <v>733.9068110594028</v>
       </c>
       <c r="N26" t="n">
-        <v>664.654907818579</v>
+        <v>609.9786599071019</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>265.4888946997207</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>298.5467080002087</v>
+        <v>87.73406121190752</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9939,7 +9939,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>62.42560738822591</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K27" t="n">
         <v>295.8802408630135</v>
@@ -9948,13 +9948,13 @@
         <v>350.4604139412999</v>
       </c>
       <c r="M27" t="n">
-        <v>467.3214504614648</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N27" t="n">
         <v>241.1347695155256</v>
       </c>
       <c r="O27" t="n">
-        <v>368.9190033132518</v>
+        <v>199.5064988049888</v>
       </c>
       <c r="P27" t="n">
         <v>219.1507118405495</v>
@@ -10106,10 +10106,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>733.9068110594037</v>
+        <v>616.7194578476444</v>
       </c>
       <c r="N29" t="n">
-        <v>547.4675546068306</v>
+        <v>664.6549078185799</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10182,7 +10182,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L30" t="n">
-        <v>130.944382706969</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M30" t="n">
         <v>471.6948204301074</v>
@@ -10191,10 +10191,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O30" t="n">
-        <v>368.9190033132527</v>
+        <v>283.2327411491641</v>
       </c>
       <c r="P30" t="n">
-        <v>24.9804809108019</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q30" t="n">
         <v>17.27519534353338</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>595.9068110594058</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N32" t="n">
-        <v>467.0433121826348</v>
+        <v>467.0433121825769</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>87.73406121190752</v>
+        <v>277.7340612119106</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10416,22 +10416,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K33" t="n">
-        <v>36.69966924109012</v>
+        <v>226.6996692410932</v>
       </c>
       <c r="L33" t="n">
-        <v>22.46041394129978</v>
+        <v>39.74451172496054</v>
       </c>
       <c r="M33" t="n">
-        <v>295.2088760493218</v>
+        <v>467.9247782656062</v>
       </c>
       <c r="N33" t="n">
         <v>431.1347695155287</v>
       </c>
       <c r="O33" t="n">
-        <v>230.9190033132547</v>
+        <v>40.91900331325166</v>
       </c>
       <c r="P33" t="n">
-        <v>214.9804809108049</v>
+        <v>24.9804809108019</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10583,7 +10583,7 @@
         <v>405.9068110594027</v>
       </c>
       <c r="N35" t="n">
-        <v>336.654907818579</v>
+        <v>415.5079586472265</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.5871120406128</v>
+        <v>87.73406121190752</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10653,13 +10653,13 @@
         <v>191.4256073882314</v>
       </c>
       <c r="K36" t="n">
-        <v>165.6996692410956</v>
+        <v>36.69966924109012</v>
       </c>
       <c r="L36" t="n">
-        <v>151.4604139413053</v>
+        <v>146.2482927291621</v>
       </c>
       <c r="M36" t="n">
-        <v>401.7126570535233</v>
+        <v>406.9247782656086</v>
       </c>
       <c r="N36" t="n">
         <v>241.1347695155256</v>
@@ -10668,7 +10668,7 @@
         <v>40.91900331325166</v>
       </c>
       <c r="P36" t="n">
-        <v>24.9804809108019</v>
+        <v>153.9804809108074</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>405.9068110594027</v>
+        <v>484.7598618880502</v>
       </c>
       <c r="N38" t="n">
-        <v>415.5079586472843</v>
+        <v>336.654907818579</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10887,25 +10887,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>62.42560738822591</v>
+        <v>186.2134861760774</v>
       </c>
       <c r="K39" t="n">
         <v>36.69966924109012</v>
       </c>
       <c r="L39" t="n">
-        <v>151.4604139413089</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M39" t="n">
         <v>406.9247782656122</v>
       </c>
       <c r="N39" t="n">
-        <v>370.1347695155347</v>
+        <v>241.1347695155256</v>
       </c>
       <c r="O39" t="n">
-        <v>164.706882101161</v>
+        <v>169.9190033132608</v>
       </c>
       <c r="P39" t="n">
-        <v>24.9804809108019</v>
+        <v>153.980480910811</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11057,7 +11057,7 @@
         <v>405.9068110594027</v>
       </c>
       <c r="N41" t="n">
-        <v>415.5079586472843</v>
+        <v>336.654907818579</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>87.73406121190752</v>
+        <v>166.587112040555</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,25 +11124,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>62.42560738822591</v>
+        <v>191.4256073882423</v>
       </c>
       <c r="K42" t="n">
         <v>36.69966924109012</v>
       </c>
       <c r="L42" t="n">
-        <v>22.46041394129978</v>
+        <v>151.4604139413162</v>
       </c>
       <c r="M42" t="n">
-        <v>406.9247782656195</v>
+        <v>401.7126570534327</v>
       </c>
       <c r="N42" t="n">
-        <v>370.134769515542</v>
+        <v>241.1347695155256</v>
       </c>
       <c r="O42" t="n">
-        <v>164.7068821011391</v>
+        <v>169.9190033132681</v>
       </c>
       <c r="P42" t="n">
-        <v>153.9804809108183</v>
+        <v>24.9804809108019</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11294,7 +11294,7 @@
         <v>405.9068110594027</v>
       </c>
       <c r="N44" t="n">
-        <v>399.6695748090032</v>
+        <v>399.6695748088426</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11364,19 +11364,19 @@
         <v>62.42560738822591</v>
       </c>
       <c r="K45" t="n">
-        <v>36.69966924109012</v>
+        <v>161.6996692411256</v>
       </c>
       <c r="L45" t="n">
-        <v>147.4604139413353</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M45" t="n">
-        <v>277.9247782656032</v>
+        <v>402.9247782656032</v>
       </c>
       <c r="N45" t="n">
-        <v>361.084264464972</v>
+        <v>361.0842644649496</v>
       </c>
       <c r="O45" t="n">
-        <v>165.9190033132872</v>
+        <v>40.91900331325166</v>
       </c>
       <c r="P45" t="n">
         <v>149.9804809108374</v>
@@ -22512,10 +22512,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>22.25469119856848</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
@@ -22566,10 +22566,10 @@
         <v>76.89299192292594</v>
       </c>
       <c r="T2" t="n">
-        <v>74.00717569841316</v>
+        <v>59.22637569841311</v>
       </c>
       <c r="U2" t="n">
-        <v>125.1582613727313</v>
+        <v>249.1582613727313</v>
       </c>
       <c r="V2" t="n">
         <v>105.8510241668239</v>
@@ -22703,22 +22703,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>65.22787369763188</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>74.36757049824092</v>
+        <v>66.48805588229362</v>
       </c>
       <c r="P4" t="n">
         <v>120.7006186397529</v>
       </c>
       <c r="Q4" t="n">
-        <v>172.243266425598</v>
+        <v>296.243266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>310.7100624073805</v>
+        <v>259.8174507209596</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22752,7 +22752,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -22803,19 +22803,19 @@
         <v>76.89299192292592</v>
       </c>
       <c r="T5" t="n">
-        <v>183.2263756984131</v>
+        <v>59.22637569841313</v>
       </c>
       <c r="U5" t="n">
         <v>125.1582613727313</v>
       </c>
       <c r="V5" t="n">
-        <v>105.8510241668239</v>
+        <v>173.0758349983416</v>
       </c>
       <c r="W5" t="n">
-        <v>114.3734759809475</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>86.03206604919151</v>
+        <v>68.28183346066771</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -22940,22 +22940,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>65.22787369763185</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>117.0987146159472</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>81.26885588229368</v>
+        <v>66.48805588229362</v>
       </c>
       <c r="P7" t="n">
         <v>120.7006186397529</v>
       </c>
       <c r="Q7" t="n">
-        <v>172.243266425598</v>
+        <v>245.3506547391771</v>
       </c>
       <c r="R7" t="n">
-        <v>186.7100624073806</v>
+        <v>310.7100624073806</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23037,13 +23037,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>73.89299192292592</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>180.2263756984131</v>
       </c>
       <c r="U8" t="n">
-        <v>121.3975929172756</v>
+        <v>195.2905848402016</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -23177,10 +23177,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>62.22787369763186</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>48.63698913799378</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -23189,7 +23189,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.243266425598</v>
+        <v>141.1081292612236</v>
       </c>
       <c r="R10" t="n">
         <v>44.71006240738057</v>
@@ -23226,13 +23226,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126.4211202107257</v>
+        <v>53.89141789466841</v>
       </c>
       <c r="D11" t="n">
         <v>102.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>96.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>168.8929919229259</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>12.70061863975292</v>
       </c>
       <c r="Q13" t="n">
-        <v>214.8929988099742</v>
+        <v>388.243266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>402.7100624073805</v>
+        <v>229.3597947917567</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -23460,25 +23460,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>173.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>141.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>102.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>96.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>96.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>94.96943258852374</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>88.69382889383314</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23517,19 +23517,19 @@
         <v>275.2263756984131</v>
       </c>
       <c r="U14" t="n">
-        <v>341.1582613727313</v>
+        <v>17.15826137273127</v>
       </c>
       <c r="V14" t="n">
-        <v>321.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>330.3734759809475</v>
+        <v>6.373475980947546</v>
       </c>
       <c r="X14" t="n">
-        <v>28.19563525163807</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>203.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -23602,7 +23602,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.748556743253886</v>
+        <v>1.748556743249836</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -23648,28 +23648,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>63.00034946925458</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>157.2278736976318</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>209.0987146159472</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>45.32279460154258</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>12.7006186397529</v>
       </c>
       <c r="Q16" t="n">
-        <v>64.24326642559799</v>
+        <v>388.243266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>78.71006240738058</v>
+        <v>181.1458560725079</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>48.21393871924888</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23700,7 +23700,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>49.48733978774786</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -23748,13 +23748,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>81.89299192292594</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>247.6977643934799</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>116.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23940,16 +23940,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>15.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>9.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>9.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3006568780820666</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -24003,7 +24003,7 @@
         <v>197.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>34.89273093281236</v>
       </c>
     </row>
     <row r="21">
@@ -24408,10 +24408,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>174.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>122.8994979944766</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -24420,13 +24420,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>97.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>95.96943258852377</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>92.94017126634151</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24462,7 +24462,7 @@
         <v>169.8929919229259</v>
       </c>
       <c r="T26" t="n">
-        <v>276.2263756984131</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>342.1582613727313</v>
@@ -24471,7 +24471,7 @@
         <v>322.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>66.246678669652</v>
+        <v>331.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24535,7 +24535,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.225356743197409</v>
+        <v>1.225356743253883</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -24602,7 +24602,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>149.551067380145</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -24611,10 +24611,10 @@
         <v>337.7006186397529</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.24326642559788</v>
+        <v>61.24326642558572</v>
       </c>
       <c r="R28" t="n">
-        <v>75.71006240738046</v>
+        <v>225.2611297875376</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24651,19 +24651,19 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>103.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>97.88962870801186</v>
       </c>
       <c r="G29" t="n">
         <v>95.96943258852374</v>
       </c>
       <c r="H29" t="n">
-        <v>92.94017126634148</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,13 +24696,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>169.8929919229259</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>232.6717744123931</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>14.15826137270801</v>
+        <v>211.0711249196478</v>
       </c>
       <c r="V29" t="n">
         <v>322.8510241668239</v>
@@ -24772,7 +24772,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.225356743242827</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.225356743244205</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -24836,25 +24836,25 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>144.8490727786782</v>
       </c>
       <c r="N31" t="n">
-        <v>194.0630114979259</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>283.4880558822936</v>
       </c>
       <c r="P31" t="n">
-        <v>9.700618639726372</v>
+        <v>9.700618639725917</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.24326642556935</v>
+        <v>61.24326642556889</v>
       </c>
       <c r="R31" t="n">
-        <v>75.71006240736119</v>
+        <v>75.71006240736074</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>49.21393871924888</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24882,7 +24882,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>16.99931295557451</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>105.7487082408338</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -24948,10 +24948,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>42.43196260250961</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>46.31743268280638</v>
       </c>
     </row>
     <row r="33">
@@ -25085,10 +25085,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>41.40652926122237</v>
+        <v>41.40652926128271</v>
       </c>
       <c r="R34" t="n">
-        <v>55.71006240732504</v>
+        <v>55.7100624073214</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25173,19 +25173,19 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>118.2263756984131</v>
       </c>
       <c r="U35" t="n">
-        <v>55.15826137265867</v>
+        <v>144.0266323948472</v>
       </c>
       <c r="V35" t="n">
-        <v>115.6639374266207</v>
+        <v>35.85102416675079</v>
       </c>
       <c r="W35" t="n">
-        <v>44.37347598088661</v>
+        <v>44.37347598087933</v>
       </c>
       <c r="X35" t="n">
-        <v>127.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -25310,7 +25310,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2278736976318783</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -25319,13 +25319,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>114.664189138081</v>
+        <v>50.70061863966475</v>
       </c>
       <c r="Q37" t="n">
-        <v>102.2432664255248</v>
+        <v>166.4347106216404</v>
       </c>
       <c r="R37" t="n">
-        <v>116.7100624073098</v>
+        <v>116.7100624072989</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25413,19 +25413,19 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>55.15826137263275</v>
+        <v>133.2530080932124</v>
       </c>
       <c r="V38" t="n">
-        <v>35.85102416675034</v>
+        <v>164.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>60.86964360240198</v>
+        <v>44.3734759808541</v>
       </c>
       <c r="X38" t="n">
-        <v>127.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>46.31743268280638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -25550,19 +25550,19 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>52.09871461594719</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>12.09272958018182</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>50.7006186396427</v>
+        <v>50.70061863963542</v>
       </c>
       <c r="Q40" t="n">
-        <v>102.2432664254916</v>
+        <v>102.2432664254807</v>
       </c>
       <c r="R40" t="n">
-        <v>116.7100624072841</v>
+        <v>180.9015066034881</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>236.9993129555745</v>
+        <v>107.9993129555581</v>
       </c>
       <c r="C41" t="n">
         <v>204.4745782429939</v>
@@ -25602,13 +25602,13 @@
         <v>165.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>159.3632896068686</v>
+        <v>30.36328960685228</v>
       </c>
       <c r="F41" t="n">
         <v>159.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>44.34623258890569</v>
+        <v>157.9694325885237</v>
       </c>
       <c r="H41" t="n">
         <v>154.9401712663415</v>
@@ -25653,16 +25653,16 @@
         <v>404.1582613727313</v>
       </c>
       <c r="V41" t="n">
-        <v>255.8510241666831</v>
+        <v>384.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>264.3734759807975</v>
+        <v>393.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>347.2818334606677</v>
+        <v>233.6586334607169</v>
       </c>
       <c r="Y41" t="n">
-        <v>137.3174326826586</v>
+        <v>137.31743268279</v>
       </c>
     </row>
     <row r="42">
@@ -25723,25 +25723,25 @@
         <v>276.0985520093604</v>
       </c>
       <c r="S42" t="n">
-        <v>84.73324524745368</v>
+        <v>213.7332452476302</v>
       </c>
       <c r="T42" t="n">
         <v>158.6584821986459</v>
       </c>
       <c r="U42" t="n">
-        <v>136.1956662494153</v>
+        <v>155.1826239111302</v>
       </c>
       <c r="V42" t="n">
-        <v>40.51066719137845</v>
+        <v>40.51066719136389</v>
       </c>
       <c r="W42" t="n">
-        <v>58.3731429096818</v>
+        <v>58.37314290966725</v>
       </c>
       <c r="X42" t="n">
-        <v>174.8627394453875</v>
+        <v>45.86273944523128</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.3913927661343</v>
+        <v>135.404435104485</v>
       </c>
     </row>
     <row r="43">
@@ -25751,7 +25751,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -25778,13 +25778,13 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2.457167243766001</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>126.0003494692546</v>
       </c>
       <c r="M43" t="n">
-        <v>199.485825943566</v>
+        <v>220.2278736976318</v>
       </c>
       <c r="N43" t="n">
         <v>272.0987146159472</v>
@@ -25793,16 +25793,16 @@
         <v>345.4880558822936</v>
       </c>
       <c r="P43" t="n">
-        <v>270.7006186395636</v>
+        <v>399.7006186397529</v>
       </c>
       <c r="Q43" t="n">
         <v>451.243266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>465.7100624073806</v>
+        <v>383.3035898458947</v>
       </c>
       <c r="S43" t="n">
-        <v>111.2139387192489</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25820,7 +25820,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>42.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -25839,16 +25839,16 @@
         <v>165.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>159.3632896068686</v>
+        <v>34.36328960683318</v>
       </c>
       <c r="F44" t="n">
-        <v>159.8896287080119</v>
+        <v>34.88962870797639</v>
       </c>
       <c r="G44" t="n">
-        <v>157.9694325885237</v>
+        <v>32.9694325884883</v>
       </c>
       <c r="H44" t="n">
-        <v>29.94017126630595</v>
+        <v>154.9401712663415</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25890,13 +25890,13 @@
         <v>404.1582613727313</v>
       </c>
       <c r="V44" t="n">
-        <v>259.8510241667884</v>
+        <v>274.7510241669304</v>
       </c>
       <c r="W44" t="n">
-        <v>268.373475980912</v>
+        <v>393.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>237.1818334606168</v>
+        <v>347.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>266.3174326828064</v>
@@ -25912,22 +25912,22 @@
         <v>139.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>116.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>9.342403447866388</v>
+        <v>97.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>94.63624233787687</v>
       </c>
       <c r="G45" t="n">
         <v>80.31795096936696</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>75.93415144361552</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25963,10 +25963,10 @@
         <v>213.7332452476302</v>
       </c>
       <c r="T45" t="n">
-        <v>158.6584821986459</v>
+        <v>33.65848219830883</v>
       </c>
       <c r="U45" t="n">
-        <v>155.1826239111302</v>
+        <v>30.18262391077866</v>
       </c>
       <c r="V45" t="n">
         <v>169.5106671915202</v>
@@ -25978,7 +25978,7 @@
         <v>174.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>154.3913927661343</v>
+        <v>29.39139276582176</v>
       </c>
     </row>
     <row r="46">
@@ -25991,7 +25991,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>27.72524664804467</v>
       </c>
       <c r="D46" t="n">
         <v>40.53621805555548</v>
@@ -26000,7 +26000,7 @@
         <v>35.98090483695654</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>29.38285596774193</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -26015,28 +26015,28 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2.457167243766001</v>
+        <v>2.457167243766008</v>
       </c>
       <c r="L46" t="n">
-        <v>126.0003494692546</v>
+        <v>1.000349469254587</v>
       </c>
       <c r="M46" t="n">
-        <v>187.7810328135432</v>
+        <v>220.2278736976319</v>
       </c>
       <c r="N46" t="n">
         <v>272.0987146159472</v>
       </c>
       <c r="O46" t="n">
-        <v>220.4880558822582</v>
+        <v>345.4880558822937</v>
       </c>
       <c r="P46" t="n">
-        <v>399.7006186397529</v>
+        <v>392.6803222904146</v>
       </c>
       <c r="Q46" t="n">
-        <v>451.243266425598</v>
+        <v>326.243266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>465.7100624073806</v>
+        <v>465.7100624073805</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26057,7 +26057,7 @@
         <v>2.443645430107551</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>42.46535284946236</v>
       </c>
     </row>
   </sheetData>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>975293.9735843866</v>
+        <v>975293.9735843868</v>
       </c>
     </row>
     <row r="3">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8392493.027459981</v>
+        <v>8392493.027459973</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9266534.826341456</v>
+        <v>9266534.82634145</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10204223.33527371</v>
+        <v>10204223.3352737</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11139643.28885397</v>
+        <v>11139643.28885395</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12088323.53334333</v>
+        <v>12088323.5333433</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12775920.16191483</v>
+        <v>12775920.16191479</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13461106.62521362</v>
+        <v>13461106.62521357</v>
       </c>
     </row>
   </sheetData>
@@ -26287,31 +26287,31 @@
         <v>1208668.790829702</v>
       </c>
       <c r="H2" t="n">
-        <v>1209873.546381701</v>
+        <v>1209873.546381702</v>
       </c>
       <c r="I2" t="n">
         <v>1227892.61432428</v>
       </c>
       <c r="J2" t="n">
-        <v>1099600.972786386</v>
+        <v>1099600.972786378</v>
       </c>
       <c r="K2" t="n">
         <v>1099600.972786379</v>
       </c>
       <c r="L2" t="n">
-        <v>1217412.928832665</v>
+        <v>1217412.928832659</v>
       </c>
       <c r="M2" t="n">
-        <v>1193500.952744665</v>
+        <v>1193500.95274466</v>
       </c>
       <c r="N2" t="n">
-        <v>1193500.952744665</v>
+        <v>1193500.95274466</v>
       </c>
       <c r="O2" t="n">
-        <v>865040.9198157516</v>
+        <v>865040.9198157447</v>
       </c>
       <c r="P2" t="n">
-        <v>863102.6978157599</v>
+        <v>863102.6978157446</v>
       </c>
     </row>
     <row r="3">
@@ -26345,7 +26345,7 @@
         <v>24992</v>
       </c>
       <c r="J3" t="n">
-        <v>194656.0000000052</v>
+        <v>194656</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>582227.2078207359</v>
+        <v>582219.8413731203</v>
       </c>
       <c r="C4" t="n">
-        <v>580188.050071653</v>
+        <v>580180.6836240375</v>
       </c>
       <c r="D4" t="n">
-        <v>605717.0639415308</v>
+        <v>605706.6050732387</v>
       </c>
       <c r="E4" t="n">
-        <v>545838.6133645035</v>
+        <v>545826.7968390246</v>
       </c>
       <c r="F4" t="n">
-        <v>544096.6128081323</v>
+        <v>544084.7962826537</v>
       </c>
       <c r="G4" t="n">
-        <v>605315.9923374224</v>
+        <v>605304.1758119436</v>
       </c>
       <c r="H4" t="n">
-        <v>603835.1295023952</v>
+        <v>603823.2239502156</v>
       </c>
       <c r="I4" t="n">
-        <v>609265.0071418529</v>
+        <v>609251.5213657346</v>
       </c>
       <c r="J4" t="n">
-        <v>537112.7865549515</v>
+        <v>537100.8810027686</v>
       </c>
       <c r="K4" t="n">
-        <v>535362.3027345812</v>
+        <v>535350.3971824013</v>
       </c>
       <c r="L4" t="n">
-        <v>604981.3622014411</v>
+        <v>604972.5280704353</v>
       </c>
       <c r="M4" t="n">
-        <v>591480.7049964468</v>
+        <v>591473.228522628</v>
       </c>
       <c r="N4" t="n">
-        <v>589279.010411957</v>
+        <v>589271.5339381382</v>
       </c>
       <c r="O4" t="n">
-        <v>404184.9363094284</v>
+        <v>404177.459835609</v>
       </c>
       <c r="P4" t="n">
-        <v>401819.8426883569</v>
+        <v>401812.4552412339</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>61487.048</v>
       </c>
       <c r="J5" t="n">
-        <v>50024.38300000089</v>
+        <v>50024.383</v>
       </c>
       <c r="K5" t="n">
-        <v>50024.38300000089</v>
+        <v>50024.383</v>
       </c>
       <c r="L5" t="n">
-        <v>54916.88500000089</v>
+        <v>54916.885</v>
       </c>
       <c r="M5" t="n">
-        <v>51208.08500000089</v>
+        <v>51208.085</v>
       </c>
       <c r="N5" t="n">
-        <v>51208.08500000089</v>
+        <v>51208.085</v>
       </c>
       <c r="O5" t="n">
-        <v>32712.90500000089</v>
+        <v>32712.905</v>
       </c>
       <c r="P5" t="n">
-        <v>32469.70500000089</v>
+        <v>32469.705</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>274052.2263359017</v>
+        <v>274059.5927835172</v>
       </c>
       <c r="C6" t="n">
-        <v>510839.3840849848</v>
+        <v>510846.7505326002</v>
       </c>
       <c r="D6" t="n">
-        <v>483212.5263903023</v>
+        <v>483222.9852585944</v>
       </c>
       <c r="E6" t="n">
-        <v>238142.5540207746</v>
+        <v>238154.3705462535</v>
       </c>
       <c r="F6" t="n">
-        <v>505356.5545771463</v>
+        <v>505368.3711026256</v>
       </c>
       <c r="G6" t="n">
-        <v>476573.5434922791</v>
+        <v>476585.360017758</v>
       </c>
       <c r="H6" t="n">
-        <v>547207.9618793064</v>
+        <v>547219.8674314864</v>
       </c>
       <c r="I6" t="n">
-        <v>532148.5591824272</v>
+        <v>532162.0449585457</v>
       </c>
       <c r="J6" t="n">
-        <v>317807.8032314286</v>
+        <v>317819.7087836097</v>
       </c>
       <c r="K6" t="n">
-        <v>514214.2870517972</v>
+        <v>514226.1926039775</v>
       </c>
       <c r="L6" t="n">
-        <v>361162.6816312234</v>
+        <v>361171.5157622242</v>
       </c>
       <c r="M6" t="n">
-        <v>550812.1627482173</v>
+        <v>550819.6392220316</v>
       </c>
       <c r="N6" t="n">
-        <v>553013.8573327069</v>
+        <v>553021.3338065218</v>
       </c>
       <c r="O6" t="n">
-        <v>428143.0785063223</v>
+        <v>428150.5549801358</v>
       </c>
       <c r="P6" t="n">
-        <v>428813.1501274022</v>
+        <v>428820.5375745106</v>
       </c>
     </row>
   </sheetData>
@@ -26883,25 +26883,25 @@
         <v>399</v>
       </c>
       <c r="J4" t="n">
-        <v>328.0000000000146</v>
+        <v>328</v>
       </c>
       <c r="K4" t="n">
-        <v>328.0000000000146</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>190.0000000000146</v>
+        <v>190</v>
       </c>
       <c r="M4" t="n">
-        <v>129.0000000000146</v>
+        <v>129</v>
       </c>
       <c r="N4" t="n">
-        <v>129.0000000000146</v>
+        <v>129</v>
       </c>
       <c r="O4" t="n">
-        <v>129.0000000000146</v>
+        <v>129</v>
       </c>
       <c r="P4" t="n">
-        <v>125.0000000000146</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -27100,7 +27100,7 @@
         <v>71</v>
       </c>
       <c r="J4" t="n">
-        <v>53.0000000000075</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27533,7 +27533,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I3" t="n">
-        <v>91.07586615948195</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27563,7 +27563,7 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>392.6018351623685</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27578,7 +27578,7 @@
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>295.8627394453875</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27597,19 +27597,19 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>398.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.6904302185792</v>
+        <v>368.6904302185793</v>
       </c>
       <c r="H4" t="n">
-        <v>225.6286998721104</v>
+        <v>235.1357217545215</v>
       </c>
       <c r="I4" t="n">
         <v>166.0044720135609</v>
@@ -27621,7 +27621,7 @@
         <v>247.457167243766</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>371.0003494692546</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>356.2139387192489</v>
       </c>
       <c r="T4" t="n">
-        <v>332.5144025718315</v>
+        <v>208.5144025718315</v>
       </c>
       <c r="U4" t="n">
         <v>150.9391125859333</v>
       </c>
       <c r="V4" t="n">
-        <v>245.3744973946186</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>350.3728098387097</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>371.4436454301076</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27758,10 +27758,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>235.8723501354155</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>215.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.317950969367</v>
@@ -27797,10 +27797,10 @@
         <v>119.2643216942532</v>
       </c>
       <c r="R6" t="n">
-        <v>397.0985520093604</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>334.7332452476302</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27809,10 +27809,10 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>290.5106671915202</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>346.8577884649922</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
@@ -27846,19 +27846,19 @@
         <v>244.6904302185792</v>
       </c>
       <c r="H7" t="n">
-        <v>225.6286998721104</v>
+        <v>271.8328870505129</v>
       </c>
       <c r="I7" t="n">
-        <v>166.0044720135609</v>
+        <v>290.0044720135609</v>
       </c>
       <c r="J7" t="n">
         <v>10.28055539328483</v>
       </c>
       <c r="K7" t="n">
-        <v>247.457167243766</v>
+        <v>371.457167243766</v>
       </c>
       <c r="L7" t="n">
-        <v>371.0003494692546</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>356.2139387192489</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>214.6181018988091</v>
+        <v>332.5144025718315</v>
       </c>
       <c r="U7" t="n">
-        <v>274.9391125859333</v>
+        <v>150.9391125859333</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>350.3728098387097</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>371.4436454301076</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27989,13 +27989,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>187.1960619922554</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>81.42429590917806</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28031,16 +28031,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R9" t="n">
         <v>258.0985520093604</v>
       </c>
       <c r="S9" t="n">
-        <v>403</v>
+        <v>195.7332452476302</v>
       </c>
       <c r="T9" t="n">
-        <v>403</v>
+        <v>140.6584821986459</v>
       </c>
       <c r="U9" t="n">
         <v>400.1826239111301</v>
@@ -28055,7 +28055,7 @@
         <v>403</v>
       </c>
       <c r="Y9" t="n">
-        <v>136.3913927661343</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28077,22 +28077,22 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>403</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>244.6904302185792</v>
       </c>
       <c r="H10" t="n">
-        <v>403</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I10" t="n">
-        <v>177.8340474252046</v>
+        <v>166.0044720135609</v>
       </c>
       <c r="J10" t="n">
         <v>10.28055539328483</v>
       </c>
       <c r="K10" t="n">
-        <v>403</v>
+        <v>247.457167243766</v>
       </c>
       <c r="L10" t="n">
         <v>403</v>
@@ -28116,13 +28116,13 @@
         <v>403</v>
       </c>
       <c r="S10" t="n">
-        <v>356.2139387192489</v>
+        <v>403</v>
       </c>
       <c r="T10" t="n">
-        <v>208.5144025718315</v>
+        <v>383.0283062050392</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9391125859333</v>
+        <v>403</v>
       </c>
       <c r="V10" t="n">
         <v>403</v>
@@ -28362,13 +28362,13 @@
         <v>308</v>
       </c>
       <c r="V13" t="n">
-        <v>308</v>
+        <v>277.6150749880303</v>
       </c>
       <c r="W13" t="n">
         <v>308</v>
       </c>
       <c r="X13" t="n">
-        <v>277.6150749880303</v>
+        <v>308</v>
       </c>
       <c r="Y13" t="n">
         <v>308</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>119.2643216942532</v>
+        <v>119.2643216942573</v>
       </c>
       <c r="R15" t="n">
         <v>308</v>
@@ -28560,13 +28560,13 @@
         <v>308</v>
       </c>
       <c r="I16" t="n">
-        <v>308</v>
+        <v>277.6150749880303</v>
       </c>
       <c r="J16" t="n">
         <v>308</v>
       </c>
       <c r="K16" t="n">
-        <v>277.6150749880305</v>
+        <v>308</v>
       </c>
       <c r="L16" t="n">
         <v>308</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>60.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
@@ -28706,7 +28706,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>18.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28718,7 +28718,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28745,10 +28745,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>329.1826209118519</v>
+        <v>395</v>
       </c>
       <c r="S18" t="n">
-        <v>134.7332452476302</v>
+        <v>395</v>
       </c>
       <c r="T18" t="n">
         <v>395</v>
@@ -28763,10 +28763,10 @@
         <v>395</v>
       </c>
       <c r="X18" t="n">
+        <v>194.6959673738905</v>
+      </c>
+      <c r="Y18" t="n">
         <v>395</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>75.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -28776,13 +28776,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>395</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C19" t="n">
         <v>395</v>
       </c>
       <c r="D19" t="n">
-        <v>395</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E19" t="n">
         <v>395</v>
@@ -28791,7 +28791,7 @@
         <v>395</v>
       </c>
       <c r="G19" t="n">
-        <v>395</v>
+        <v>304.1100540305886</v>
       </c>
       <c r="H19" t="n">
         <v>225.6286998721104</v>
@@ -28827,25 +28827,25 @@
         <v>395</v>
       </c>
       <c r="S19" t="n">
+        <v>356.2139387192489</v>
+      </c>
+      <c r="T19" t="n">
+        <v>208.5144025718315</v>
+      </c>
+      <c r="U19" t="n">
         <v>395</v>
-      </c>
-      <c r="T19" t="n">
-        <v>395</v>
-      </c>
-      <c r="U19" t="n">
-        <v>285.2066055960235</v>
       </c>
       <c r="V19" t="n">
         <v>395</v>
       </c>
       <c r="W19" t="n">
-        <v>226.3728098387097</v>
+        <v>395</v>
       </c>
       <c r="X19" t="n">
-        <v>247.4436454301076</v>
+        <v>395</v>
       </c>
       <c r="Y19" t="n">
-        <v>287.4653528494624</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20">
@@ -28934,16 +28934,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>56.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>33.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>110.151573493153</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>395</v>
@@ -28991,10 +28991,10 @@
         <v>395</v>
       </c>
       <c r="U21" t="n">
-        <v>391.5170529135029</v>
+        <v>72.18262391113015</v>
       </c>
       <c r="V21" t="n">
-        <v>395</v>
+        <v>86.51066719152016</v>
       </c>
       <c r="W21" t="n">
         <v>395</v>
@@ -29003,7 +29003,7 @@
         <v>395</v>
       </c>
       <c r="Y21" t="n">
-        <v>71.39139276613435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22">
@@ -29025,13 +29025,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F22" t="n">
-        <v>274.3828559677419</v>
+        <v>395</v>
       </c>
       <c r="G22" t="n">
         <v>395</v>
       </c>
       <c r="H22" t="n">
-        <v>395</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I22" t="n">
         <v>395</v>
@@ -29040,10 +29040,10 @@
         <v>10.28055539328483</v>
       </c>
       <c r="K22" t="n">
-        <v>395</v>
+        <v>247.457167243766</v>
       </c>
       <c r="L22" t="n">
-        <v>395</v>
+        <v>371.0003494692546</v>
       </c>
       <c r="M22" t="n">
         <v>395</v>
@@ -29064,7 +29064,7 @@
         <v>395</v>
       </c>
       <c r="S22" t="n">
-        <v>395</v>
+        <v>356.2139387192489</v>
       </c>
       <c r="T22" t="n">
         <v>208.5144025718315</v>
@@ -29073,16 +29073,16 @@
         <v>395</v>
       </c>
       <c r="V22" t="n">
-        <v>260.6230189640476</v>
+        <v>395</v>
       </c>
       <c r="W22" t="n">
-        <v>226.3728098387097</v>
+        <v>311.0568220467644</v>
       </c>
       <c r="X22" t="n">
-        <v>247.4436454301076</v>
+        <v>395</v>
       </c>
       <c r="Y22" t="n">
-        <v>395</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="23">
@@ -29113,7 +29113,7 @@
         <v>392</v>
       </c>
       <c r="I23" t="n">
-        <v>119.704114456554</v>
+        <v>118.3418788500341</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>200.0209461363405</v>
+        <v>201.3831817428673</v>
       </c>
       <c r="S23" t="n">
         <v>392</v>
@@ -29174,16 +29174,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>135.9211006067155</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>325.317950969367</v>
@@ -29228,13 +29228,13 @@
         <v>392</v>
       </c>
       <c r="U24" t="n">
-        <v>214.3634488242619</v>
+        <v>392</v>
       </c>
       <c r="V24" t="n">
-        <v>15.5106671915195</v>
+        <v>392</v>
       </c>
       <c r="W24" t="n">
-        <v>33.37314290982786</v>
+        <v>392</v>
       </c>
       <c r="X24" t="n">
         <v>392</v>
@@ -29253,10 +29253,10 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C25" t="n">
-        <v>392</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D25" t="n">
-        <v>285.5362180555555</v>
+        <v>289.2661619513198</v>
       </c>
       <c r="E25" t="n">
         <v>392</v>
@@ -29274,7 +29274,7 @@
         <v>392</v>
       </c>
       <c r="J25" t="n">
-        <v>276.4551905438091</v>
+        <v>392</v>
       </c>
       <c r="K25" t="n">
         <v>392</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>119.2643216942532</v>
+        <v>119.2643216942644</v>
       </c>
       <c r="R30" t="n">
         <v>307</v>
@@ -29897,7 +29897,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>135.3179509693639</v>
+        <v>325.317950969367</v>
       </c>
       <c r="H33" t="n">
         <v>328.0964645449117</v>
@@ -29933,13 +29933,13 @@
         <v>331.0985520093574</v>
       </c>
       <c r="S33" t="n">
-        <v>410.6455669418358</v>
+        <v>268.7332452476272</v>
       </c>
       <c r="T33" t="n">
-        <v>403.6584821986459</v>
+        <v>213.6584821986428</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1826239111301</v>
+        <v>352.0949456053925</v>
       </c>
       <c r="V33" t="n">
         <v>414.5106671915202</v>
@@ -29948,7 +29948,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>229.8627394453845</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -29961,13 +29961,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>465</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C34" t="n">
-        <v>287.698497363963</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D34" t="n">
-        <v>465</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E34" t="n">
         <v>280.9809048369565</v>
@@ -29976,7 +29976,7 @@
         <v>464.3828559677449</v>
       </c>
       <c r="G34" t="n">
-        <v>434.6904302185823</v>
+        <v>244.6904302185792</v>
       </c>
       <c r="H34" t="n">
         <v>225.6286998721104</v>
@@ -30012,7 +30012,7 @@
         <v>465</v>
       </c>
       <c r="S34" t="n">
-        <v>356.2139387192489</v>
+        <v>465</v>
       </c>
       <c r="T34" t="n">
         <v>208.5144025718315</v>
@@ -30021,13 +30021,13 @@
         <v>150.9391125859333</v>
       </c>
       <c r="V34" t="n">
-        <v>199.1703102162162</v>
+        <v>389.1703102162193</v>
       </c>
       <c r="W34" t="n">
-        <v>226.3728098387097</v>
+        <v>299.9099808811818</v>
       </c>
       <c r="X34" t="n">
-        <v>247.4436454301076</v>
+        <v>437.4436454301106</v>
       </c>
       <c r="Y34" t="n">
         <v>287.4653528494624</v>
@@ -30134,13 +30134,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>196.3179509693615</v>
+        <v>325.317950969367</v>
       </c>
       <c r="H36" t="n">
         <v>328.0964645449117</v>
       </c>
       <c r="I36" t="n">
-        <v>202.6112915517259</v>
+        <v>73.6112915517204</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30167,13 +30167,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>392.098552009355</v>
+        <v>397.7396737036246</v>
       </c>
       <c r="S36" t="n">
-        <v>458.7332452476302</v>
+        <v>329.7332452476247</v>
       </c>
       <c r="T36" t="n">
-        <v>280.2996038928534</v>
+        <v>403.6584821986459</v>
       </c>
       <c r="U36" t="n">
         <v>400.1826239111301</v>
@@ -30207,28 +30207,28 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E37" t="n">
-        <v>409.980904836962</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
-        <v>373.6904302185847</v>
+        <v>244.6904302185792</v>
       </c>
       <c r="H37" t="n">
-        <v>225.6286998721104</v>
+        <v>354.6286998721159</v>
       </c>
       <c r="I37" t="n">
-        <v>166.0044720135609</v>
+        <v>295.0044720135664</v>
       </c>
       <c r="J37" t="n">
         <v>10.28055539328483</v>
       </c>
       <c r="K37" t="n">
-        <v>371.2450460316862</v>
+        <v>376.4571672437715</v>
       </c>
       <c r="L37" t="n">
-        <v>371.0003494692546</v>
+        <v>465</v>
       </c>
       <c r="M37" t="n">
         <v>465</v>
@@ -30255,10 +30255,10 @@
         <v>208.5144025718315</v>
       </c>
       <c r="U37" t="n">
-        <v>279.9391125859389</v>
+        <v>150.9391125859333</v>
       </c>
       <c r="V37" t="n">
-        <v>199.1703102162162</v>
+        <v>228.958538473333</v>
       </c>
       <c r="W37" t="n">
         <v>226.3728098387097</v>
@@ -30362,7 +30362,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>218.9376868976935</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30374,10 +30374,10 @@
         <v>325.317950969367</v>
       </c>
       <c r="H39" t="n">
-        <v>328.0964645449117</v>
+        <v>260.8361382485436</v>
       </c>
       <c r="I39" t="n">
-        <v>73.61129155171676</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30407,7 +30407,7 @@
         <v>465</v>
       </c>
       <c r="S39" t="n">
-        <v>391.4729189512054</v>
+        <v>458.7332452476302</v>
       </c>
       <c r="T39" t="n">
         <v>403.6584821986459</v>
@@ -30416,10 +30416,10 @@
         <v>400.1826239111301</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>285.5106671915111</v>
       </c>
       <c r="W39" t="n">
-        <v>432.3731429098285</v>
+        <v>303.3731429098194</v>
       </c>
       <c r="X39" t="n">
         <v>419.8627394453875</v>
@@ -30438,10 +30438,10 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>401.7252466480538</v>
       </c>
       <c r="D40" t="n">
-        <v>285.5362180555555</v>
+        <v>335.5383850319195</v>
       </c>
       <c r="E40" t="n">
         <v>280.9809048369565</v>
@@ -30465,7 +30465,7 @@
         <v>247.457167243766</v>
       </c>
       <c r="L40" t="n">
-        <v>371.0003494692546</v>
+        <v>465</v>
       </c>
       <c r="M40" t="n">
         <v>465</v>
@@ -30486,7 +30486,7 @@
         <v>465</v>
       </c>
       <c r="S40" t="n">
-        <v>356.2139387192489</v>
+        <v>465</v>
       </c>
       <c r="T40" t="n">
         <v>337.5144025718407</v>
@@ -30498,13 +30498,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>355.3728098387188</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
-        <v>376.4436454301167</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>411.2532316373716</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30933,7 +30933,7 @@
         <v>245</v>
       </c>
       <c r="J46" t="n">
-        <v>135.2805553933203</v>
+        <v>135.2805553932848</v>
       </c>
       <c r="K46" t="n">
         <v>245</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>124</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M3" t="n">
         <v>124</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>118.989898989899</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34883,19 +34883,19 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>9.507021882411044</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -34907,7 +34907,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>28.99965053074544</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>43.78606128075114</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>46.20418717840242</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34992,16 +34992,16 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>48.41751852767482</v>
       </c>
       <c r="O5" t="n">
         <v>62.51110530027941</v>
       </c>
       <c r="P5" t="n">
-        <v>113.0196535271578</v>
+        <v>124</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.39786500051702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,7 +35059,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>118.989898989899</v>
+        <v>124</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -35074,10 +35074,10 @@
         <v>124</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>118.989898989899</v>
       </c>
       <c r="P6" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -35132,19 +35132,19 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>46.20418717840248</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>28.99965053074542</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>43.78606128075112</v>
       </c>
       <c r="T7" t="n">
-        <v>6.103699326977659</v>
+        <v>124</v>
       </c>
       <c r="U7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35226,7 +35226,7 @@
         <v>124.3427939698493</v>
       </c>
       <c r="M8" t="n">
-        <v>83.43890941450614</v>
+        <v>263</v>
       </c>
       <c r="N8" t="n">
         <v>263</v>
@@ -35238,7 +35238,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q8" t="n">
-        <v>263</v>
+        <v>83.43890941450614</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,13 +35296,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K9" t="n">
         <v>259.1805716219234</v>
       </c>
       <c r="L9" t="n">
-        <v>81.14936593148506</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>193.7700421645043</v>
@@ -35311,7 +35311,7 @@
         <v>244.2737576558247</v>
       </c>
       <c r="O9" t="n">
-        <v>263</v>
+        <v>179.1102313919227</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -35363,22 +35363,22 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>128.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>177.3713001278896</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>11.82957541164369</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>155.542832756234</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>31.99965053074542</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>46.78606128075112</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>174.5139036332077</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>252.0608874140667</v>
       </c>
       <c r="V10" t="n">
         <v>203.8296897837838</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>31.8323907398343</v>
+      </c>
+      <c r="K11" t="n">
         <v>324</v>
-      </c>
-      <c r="K11" t="n">
-        <v>100.2288844221105</v>
       </c>
       <c r="L11" t="n">
         <v>124.3427939698493</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="N11" t="n">
-        <v>234.8066536896941</v>
+        <v>303.2031473719702</v>
       </c>
       <c r="O11" t="n">
         <v>62.51110530027941</v>
@@ -35475,7 +35475,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q11" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35542,13 +35542,13 @@
         <v>324</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>193.7700421645043</v>
       </c>
       <c r="N12" t="n">
         <v>244.2737576558247</v>
       </c>
       <c r="O12" t="n">
-        <v>290.4156270917803</v>
+        <v>96.64558492727613</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -35648,13 +35648,13 @@
         <v>157.0608874140667</v>
       </c>
       <c r="V13" t="n">
-        <v>108.8296897837838</v>
+        <v>78.44476477181411</v>
       </c>
       <c r="W13" t="n">
         <v>81.62719016129032</v>
       </c>
       <c r="X13" t="n">
-        <v>30.17142955792273</v>
+        <v>60.55635456989245</v>
       </c>
       <c r="Y13" t="n">
         <v>20.53464715053764</v>
@@ -35691,16 +35691,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
+        <v>31.8323907398343</v>
+      </c>
+      <c r="K14" t="n">
+        <v>100.2288844221106</v>
+      </c>
+      <c r="L14" t="n">
+        <v>124.3427939698492</v>
+      </c>
+      <c r="M14" t="n">
         <v>324</v>
-      </c>
-      <c r="K14" t="n">
-        <v>100.2288844221105</v>
-      </c>
-      <c r="L14" t="n">
-        <v>124.3427939698493</v>
-      </c>
-      <c r="M14" t="n">
-        <v>234.8066536896941</v>
       </c>
       <c r="N14" t="n">
         <v>324</v>
@@ -35712,7 +35712,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>202.9742629498597</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35791,7 +35791,7 @@
         <v>194.1702309297476</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.134066826240583e-12</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35846,13 +35846,13 @@
         <v>82.37130012788958</v>
       </c>
       <c r="I16" t="n">
-        <v>141.9955279864391</v>
+        <v>111.6106029744694</v>
       </c>
       <c r="J16" t="n">
         <v>297.7194446067152</v>
       </c>
       <c r="K16" t="n">
-        <v>30.15790774426446</v>
+        <v>60.542832756234</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>31.8323907398343</v>
+      </c>
+      <c r="K17" t="n">
+        <v>100.2288844221106</v>
+      </c>
+      <c r="L17" t="n">
+        <v>124.3427939698492</v>
+      </c>
+      <c r="M17" t="n">
         <v>324</v>
       </c>
-      <c r="K17" t="n">
-        <v>100.2288844221105</v>
-      </c>
-      <c r="L17" t="n">
-        <v>124.3427939698493</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
-        <v>234.8066536896941</v>
+        <v>202.9742629498597</v>
       </c>
       <c r="O17" t="n">
         <v>62.51110530027941</v>
@@ -36010,10 +36010,10 @@
         <v>165.0391345395625</v>
       </c>
       <c r="K18" t="n">
-        <v>259.1805716219234</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="M18" t="n">
         <v>193.7700421645043</v>
@@ -36022,10 +36022,10 @@
         <v>244.2737576558247</v>
       </c>
       <c r="O18" t="n">
-        <v>226.4753539975285</v>
+        <v>324</v>
       </c>
       <c r="P18" t="n">
-        <v>194.1702309297476</v>
+        <v>31.8261565491995</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36062,13 +36062,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>107.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>122.2747533519553</v>
       </c>
       <c r="D19" t="n">
-        <v>109.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>114.0190951630435</v>
@@ -36077,7 +36077,7 @@
         <v>120.6171440322581</v>
       </c>
       <c r="G19" t="n">
-        <v>150.3095697814208</v>
+        <v>59.41962381200943</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -36113,25 +36113,25 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>38.78606128075114</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>186.4855974281685</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>134.2674930100901</v>
+        <v>244.0608874140667</v>
       </c>
       <c r="V19" t="n">
         <v>195.8296897837838</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>168.6271901612903</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>147.5563545698924</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>107.5346471505376</v>
       </c>
     </row>
     <row r="20">
@@ -36168,16 +36168,16 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K20" t="n">
-        <v>100.2288844221106</v>
+        <v>328</v>
       </c>
       <c r="L20" t="n">
-        <v>124.3427939698492</v>
+        <v>124.3427939698493</v>
       </c>
       <c r="M20" t="n">
-        <v>328</v>
+        <v>328.0000000000005</v>
       </c>
       <c r="N20" t="n">
-        <v>210.8126467882435</v>
+        <v>311.0415312103536</v>
       </c>
       <c r="O20" t="n">
         <v>62.51110530027941</v>
@@ -36186,7 +36186,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q20" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36250,19 +36250,19 @@
         <v>259.1805716219234</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>158.5874954917371</v>
       </c>
       <c r="M21" t="n">
         <v>193.7700421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>244.2737576558247</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>328</v>
       </c>
       <c r="P21" t="n">
-        <v>108.48396876566</v>
+        <v>194.1702309297476</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36311,13 +36311,13 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>120.6171440322581</v>
       </c>
       <c r="G22" t="n">
         <v>150.3095697814208</v>
       </c>
       <c r="H22" t="n">
-        <v>169.3713001278896</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>228.9955279864391</v>
@@ -36326,10 +36326,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>147.542832756234</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>23.99965053074544</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -36350,7 +36350,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>38.78606128075114</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -36359,16 +36359,16 @@
         <v>244.0608874140667</v>
       </c>
       <c r="V22" t="n">
-        <v>61.45270874783134</v>
+        <v>195.8296897837838</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>84.68401220805475</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>147.5563545698924</v>
       </c>
       <c r="Y22" t="n">
-        <v>107.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -36405,13 +36405,13 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K23" t="n">
-        <v>100.2288844221106</v>
+        <v>399</v>
       </c>
       <c r="L23" t="n">
         <v>124.3427939698493</v>
       </c>
       <c r="M23" t="n">
-        <v>349.9439599195626</v>
+        <v>399.0000000000007</v>
       </c>
       <c r="N23" t="n">
         <v>399.0000000000007</v>
@@ -36423,7 +36423,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q23" t="n">
-        <v>399.0000000000007</v>
+        <v>51.17284434166579</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36481,7 +36481,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>165.0391345395625</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>259.1805716219234</v>
@@ -36493,10 +36493,10 @@
         <v>193.7700421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>244.2737576558247</v>
+        <v>225.3662251564623</v>
       </c>
       <c r="O24" t="n">
-        <v>157.8161284487346</v>
+        <v>341.7627954876521</v>
       </c>
       <c r="P24" t="n">
         <v>194.1702309297476</v>
@@ -36539,10 +36539,10 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>119.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>3.729943895764319</v>
       </c>
       <c r="E25" t="n">
         <v>111.0190951630435</v>
@@ -36560,7 +36560,7 @@
         <v>225.9955279864391</v>
       </c>
       <c r="J25" t="n">
-        <v>266.1746351505243</v>
+        <v>381.7194446067152</v>
       </c>
       <c r="K25" t="n">
         <v>144.542832756234</v>
@@ -36642,25 +36642,25 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K26" t="n">
-        <v>100.2288844221105</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L26" t="n">
-        <v>124.3427939698493</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M26" t="n">
         <v>328.0000000000001</v>
       </c>
       <c r="N26" t="n">
+        <v>273.3237520885229</v>
+      </c>
+      <c r="O26" t="n">
         <v>328.0000000000001</v>
-      </c>
-      <c r="O26" t="n">
-        <v>62.51110530027941</v>
       </c>
       <c r="P26" t="n">
         <v>113.0196535271578</v>
       </c>
       <c r="Q26" t="n">
-        <v>210.8126467883012</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36718,7 +36718,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K27" t="n">
         <v>259.1805716219234</v>
@@ -36727,13 +36727,13 @@
         <v>328.0000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>189.3966721958616</v>
+        <v>193.7700421645043</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>328.0000000000001</v>
+        <v>158.5874954917371</v>
       </c>
       <c r="P27" t="n">
         <v>194.1702309297476</v>
@@ -36788,7 +36788,7 @@
         <v>32.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>62.30956978142078</v>
+        <v>62.30956978142079</v>
       </c>
       <c r="H28" t="n">
         <v>81.37130012788958</v>
@@ -36800,7 +36800,7 @@
         <v>296.7194446067152</v>
       </c>
       <c r="K28" t="n">
-        <v>59.54283275623399</v>
+        <v>59.542832756234</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36879,16 +36879,16 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K29" t="n">
-        <v>100.2288844221105</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L29" t="n">
-        <v>124.3427939698493</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M29" t="n">
+        <v>210.8126467882416</v>
+      </c>
+      <c r="N29" t="n">
         <v>328.000000000001</v>
-      </c>
-      <c r="N29" t="n">
-        <v>210.8126467882517</v>
       </c>
       <c r="O29" t="n">
         <v>62.51110530027941</v>
@@ -36961,7 +36961,7 @@
         <v>259.1805716219234</v>
       </c>
       <c r="L30" t="n">
-        <v>108.4839687656692</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>193.7700421645043</v>
@@ -36970,13 +36970,13 @@
         <v>244.2737576558247</v>
       </c>
       <c r="O30" t="n">
-        <v>328.000000000001</v>
+        <v>242.3137378359124</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>194.1702309297476</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.125384858254381e-11</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37122,10 +37122,10 @@
         <v>124.3427939698493</v>
       </c>
       <c r="M32" t="n">
-        <v>190.000000000003</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>130.3884043640559</v>
+        <v>130.3884043639979</v>
       </c>
       <c r="O32" t="n">
         <v>62.51110530027941</v>
@@ -37134,7 +37134,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37195,22 +37195,22 @@
         <v>165.0391345395625</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>17.28409778366076</v>
       </c>
       <c r="M33" t="n">
-        <v>17.28409778371861</v>
+        <v>190.000000000003</v>
       </c>
       <c r="N33" t="n">
         <v>190.000000000003</v>
       </c>
       <c r="O33" t="n">
-        <v>190.000000000003</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>190.000000000003</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37247,13 +37247,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>177.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>14.97325071591832</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>179.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -37262,58 +37262,58 @@
         <v>190.000000000003</v>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>108.7860612807511</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>190.000000000003</v>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>73.5371710424721</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -37353,16 +37353,16 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K35" t="n">
-        <v>100.2288844221105</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L35" t="n">
-        <v>124.3427939698493</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>78.85305082864747</v>
       </c>
       <c r="O35" t="n">
         <v>62.51110530027941</v>
@@ -37371,7 +37371,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q35" t="n">
-        <v>78.85305082870529</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37432,22 +37432,22 @@
         <v>129.0000000000055</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>123.7878787878623</v>
+      </c>
+      <c r="M36" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>129.0000000000055</v>
-      </c>
-      <c r="M36" t="n">
-        <v>123.7878787879202</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37493,28 +37493,28 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>123.7878787879202</v>
+        <v>129.0000000000055</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>93.99965053074544</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37541,10 +37541,10 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>129.0000000000055</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>29.78822825711685</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -37590,16 +37590,16 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K38" t="n">
-        <v>100.2288844221105</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L38" t="n">
-        <v>124.3427939698493</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>78.85305082864747</v>
       </c>
       <c r="N38" t="n">
-        <v>78.85305082870529</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>62.51110530027941</v>
@@ -37666,25 +37666,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>123.7878787878515</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>129.0000000000091</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>129.0000000000091</v>
       </c>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>129.0000000000091</v>
       </c>
-      <c r="O39" t="n">
-        <v>123.7878787879093</v>
-      </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37724,10 +37724,10 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>50.00216697636401</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -37751,7 +37751,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>93.99965053074541</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37772,7 +37772,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>108.7860612807511</v>
       </c>
       <c r="T40" t="n">
         <v>129.0000000000091</v>
@@ -37784,13 +37784,13 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>129.0000000000091</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>129.0000000000091</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>123.7878787879093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37827,16 +37827,16 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K41" t="n">
-        <v>100.2288844221105</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L41" t="n">
-        <v>124.3427939698493</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>78.85305082870529</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>62.51110530027941</v>
@@ -37845,7 +37845,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>78.85305082864753</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,25 +37903,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>129.0000000000164</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>129.0000000000164</v>
       </c>
       <c r="M42" t="n">
+        <v>123.7878787878296</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>129.0000000000164</v>
       </c>
-      <c r="N42" t="n">
-        <v>129.0000000000164</v>
-      </c>
-      <c r="O42" t="n">
-        <v>123.7878787878874</v>
-      </c>
       <c r="P42" t="n">
-        <v>129.0000000000164</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38064,16 +38064,16 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K44" t="n">
-        <v>100.2288844221105</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L44" t="n">
-        <v>124.3427939698493</v>
+        <v>124.3427939698492</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>63.01466699042422</v>
+        <v>63.01466699026363</v>
       </c>
       <c r="O44" t="n">
         <v>62.51110530027941</v>
@@ -38143,19 +38143,19 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>125.0000000000355</v>
       </c>
       <c r="L45" t="n">
-        <v>125.0000000000355</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="N45" t="n">
-        <v>119.9494949494463</v>
+        <v>119.949494949424</v>
       </c>
       <c r="O45" t="n">
-        <v>125.0000000000355</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>125.0000000000355</v>
@@ -38210,7 +38210,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3095697814207878</v>
+        <v>0.3095697814207767</v>
       </c>
       <c r="H46" t="n">
         <v>19.37130012788958</v>
@@ -38219,7 +38219,7 @@
         <v>78.9955279864391</v>
       </c>
       <c r="J46" t="n">
-        <v>125.0000000000355</v>
+        <v>125</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
